--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ingse\OneDrive\Desktop\Universitaria_de_colombia\PRUEBAS DE SOFTWARE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Profesor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6656E7-DB29-4C97-9772-D5D7403B8FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B26D046-3C22-4F67-8049-8C45D6313351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pruebas_software" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="161">
   <si>
     <t>Nombre</t>
   </si>
@@ -527,7 +527,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -552,6 +552,13 @@
     <font>
       <sz val="12"/>
       <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -597,65 +604,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{76DA0987-FBEF-4C70-87A1-053D0C331F7E}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="2">
     <dxf>
       <font>
         <color theme="9"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9"/>
@@ -1078,7 +1046,7 @@
       <c r="W1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="X1" s="2" t="s">
         <v>158</v>
       </c>
     </row>
@@ -1092,66 +1060,66 @@
       <c r="C2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W2" s="7" t="s">
+      <c r="D2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W2" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X2" s="3">
-        <f>COUNTBLANK(D2:W2)</f>
+        <f t="shared" ref="X2:X26" si="0">COUNTBLANK(D2:W2)</f>
         <v>1</v>
       </c>
     </row>
@@ -1165,68 +1133,68 @@
       <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W3" s="7" t="s">
+      <c r="D3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W3" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X3" s="3">
-        <f>COUNTBLANK(D3:W3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1240,64 +1208,64 @@
       <c r="C4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W4" s="7" t="s">
+      <c r="D4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W4" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X4" s="3">
-        <f>COUNTBLANK(D4:W4)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -1311,68 +1279,68 @@
       <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W5" s="7" t="s">
+      <c r="D5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W5" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X5" s="3">
-        <f>COUNTBLANK(D5:W5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1386,66 +1354,66 @@
       <c r="C6" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W6" s="7" t="s">
+      <c r="D6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W6" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X6" s="3">
-        <f>COUNTBLANK(D6:W6)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1459,68 +1427,68 @@
       <c r="C7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W7" s="7" t="s">
+      <c r="D7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W7" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X7" s="3">
-        <f>COUNTBLANK(D7:W7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1534,68 +1502,68 @@
       <c r="C8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W8" s="7" t="s">
+      <c r="D8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W8" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X8" s="3">
-        <f>COUNTBLANK(D8:W8)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1609,66 +1577,66 @@
       <c r="C9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W9" s="7" t="s">
+      <c r="D9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W9" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X9" s="3">
-        <f>COUNTBLANK(D9:W9)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1682,68 +1650,68 @@
       <c r="C10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W10" s="7" t="s">
+      <c r="D10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W10" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X10" s="3">
-        <f>COUNTBLANK(D10:W10)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1757,66 +1725,66 @@
       <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W11" s="7" t="s">
+      <c r="D11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W11" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X11" s="3">
-        <f>COUNTBLANK(D11:W11)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1830,68 +1798,68 @@
       <c r="C12" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W12" s="7" t="s">
+      <c r="D12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V12" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W12" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X12" s="3">
-        <f>COUNTBLANK(D12:W12)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1905,66 +1873,66 @@
       <c r="C13" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W13" s="7" t="s">
+      <c r="D13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W13" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X13" s="3">
-        <f>COUNTBLANK(D13:W13)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1978,66 +1946,66 @@
       <c r="C14" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W14" s="7" t="s">
+      <c r="D14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W14" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X14" s="3">
-        <f>COUNTBLANK(D14:W14)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2051,66 +2019,66 @@
       <c r="C15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V15" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W15" s="7" t="s">
+      <c r="D15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W15" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X15" s="3">
-        <f>COUNTBLANK(D15:W15)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2124,68 +2092,68 @@
       <c r="C16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V16" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W16" s="7" t="s">
+      <c r="D16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W16" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X16" s="3">
-        <f>COUNTBLANK(D16:W16)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2199,68 +2167,68 @@
       <c r="C17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W17" s="7" t="s">
+      <c r="D17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W17" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X17" s="3">
-        <f>COUNTBLANK(D17:W17)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2274,68 +2242,68 @@
       <c r="C18" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W18" s="7" t="s">
+      <c r="D18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W18" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X18" s="3">
-        <f>COUNTBLANK(D18:W18)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2349,68 +2317,68 @@
       <c r="C19" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W19" s="7" t="s">
+      <c r="D19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W19" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X19" s="3">
-        <f>COUNTBLANK(D19:W19)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2424,66 +2392,66 @@
       <c r="C20" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W20" s="7" t="s">
+      <c r="D20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W20" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X20" s="3">
-        <f>COUNTBLANK(D20:W20)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2497,66 +2465,66 @@
       <c r="C21" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W21" s="7" t="s">
+      <c r="D21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W21" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X21" s="3">
-        <f>COUNTBLANK(D21:W21)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2570,66 +2538,66 @@
       <c r="C22" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W22" s="7" t="s">
+      <c r="D22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W22" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X22" s="3">
-        <f>COUNTBLANK(D22:W22)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2643,66 +2611,66 @@
       <c r="C23" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W23" s="7" t="s">
+      <c r="D23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W23" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X23" s="3">
-        <f>COUNTBLANK(D23:W23)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2716,64 +2684,64 @@
       <c r="C24" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V24" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W24" s="7" t="s">
+      <c r="D24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W24" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X24" s="3">
-        <f>COUNTBLANK(D24:W24)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2787,68 +2755,68 @@
       <c r="C25" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V25" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W25" s="7" t="s">
+      <c r="D25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W25" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X25" s="3">
-        <f>COUNTBLANK(D25:W25)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2862,68 +2830,68 @@
       <c r="C26" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="M26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="N26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="P26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="R26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="U26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="V26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="W26" s="7" t="s">
+      <c r="D26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="R26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="T26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="W26" s="6" t="s">
         <v>159</v>
       </c>
       <c r="X26" s="3">
-        <f>COUNTBLANK(D26:W26)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2935,7 +2903,7 @@
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D2:W26">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",D2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2955,7 +2923,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC8DBC52-987A-4412-B43F-A9A2EA19A4E3}">
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.375" bestFit="1" customWidth="1"/>
@@ -2964,7 +2932,7 @@
     <col min="4" max="24" width="4.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="100.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" ht="100.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3034,19 +3002,19 @@
       <c r="W1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="X1" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>159</v>
@@ -3113,15 +3081,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>159</v>
@@ -3187,16 +3155,17 @@
         <f t="shared" ref="X3:X22" si="0">COUNTBLANK(D3:W3)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Z3" s="7"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>159</v>
@@ -3263,15 +3232,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>159</v>
@@ -3288,9 +3257,7 @@
       <c r="H5" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
         <v>159</v>
       </c>
@@ -3335,30 +3302,32 @@
       </c>
       <c r="X5" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="G6" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="H6" s="5"/>
       <c r="I6" s="5" t="s">
         <v>159</v>
       </c>
@@ -3406,18 +3375,18 @@
       </c>
       <c r="X6" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>159</v>
@@ -3484,15 +3453,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>159</v>
@@ -3503,8 +3472,12 @@
       <c r="F8" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="G8" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="I8" s="5" t="s">
         <v>159</v>
       </c>
@@ -3552,18 +3525,18 @@
       </c>
       <c r="X8" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>159</v>
@@ -3572,12 +3545,8 @@
         <v>159</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
       <c r="I9" s="5" t="s">
         <v>159</v>
       </c>
@@ -3625,10 +3594,10 @@
       </c>
       <c r="X9" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>148</v>
       </c>
@@ -3703,15 +3672,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>159</v>
@@ -3719,9 +3688,15 @@
       <c r="E11" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+      <c r="F11" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="I11" s="5" t="s">
         <v>159</v>
       </c>
@@ -3769,29 +3744,27 @@
       </c>
       <c r="X11" s="3">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="G12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="H12" s="5" t="s">
         <v>159</v>
       </c>
@@ -3842,18 +3815,18 @@
       </c>
       <c r="X12" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>159</v>
@@ -3920,15 +3893,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>159</v>
@@ -3939,12 +3912,8 @@
       <c r="F14" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
       <c r="I14" s="5" t="s">
         <v>159</v>
       </c>
@@ -3992,34 +3961,28 @@
       </c>
       <c r="X14" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
       <c r="G15" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H15" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="H15" s="5"/>
       <c r="I15" s="5" t="s">
         <v>159</v>
       </c>
@@ -4067,18 +4030,18 @@
       </c>
       <c r="X15" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>159</v>
@@ -4092,7 +4055,9 @@
       <c r="G16" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H16" s="5"/>
+      <c r="H16" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="I16" s="5" t="s">
         <v>159</v>
       </c>
@@ -4140,18 +4105,18 @@
       </c>
       <c r="X16" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>159</v>
@@ -4220,13 +4185,13 @@
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>159</v>
@@ -4234,9 +4199,7 @@
       <c r="E18" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
         <v>159</v>
       </c>
@@ -4290,18 +4253,18 @@
       </c>
       <c r="X18" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>159</v>
@@ -4370,13 +4333,13 @@
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>159</v>
@@ -4445,23 +4408,27 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="H21" s="5"/>
+      <c r="E21" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="I21" s="5" t="s">
         <v>159</v>
       </c>
@@ -4509,18 +4476,18 @@
       </c>
       <c r="X21" s="3">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>159</v>
@@ -4590,11 +4557,11 @@
   </sheetData>
   <autoFilter ref="A1:W1" xr:uid="{AC8DBC52-987A-4412-B43F-A9A2EA19A4E3}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W22">
-      <sortCondition ref="C1"/>
+      <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="D2:W22">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"x"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Profesor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B26D046-3C22-4F67-8049-8C45D6313351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFA9E77-6085-4335-A3F7-2279506D6D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="161">
   <si>
     <t>Nombre</t>
   </si>
@@ -3257,7 +3257,9 @@
       <c r="H5" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="I5" s="5"/>
+      <c r="I5" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="J5" s="5" t="s">
         <v>159</v>
       </c>
@@ -3302,7 +3304,7 @@
       </c>
       <c r="X5" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -3403,9 +3405,7 @@
       <c r="H7" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="I7" s="5"/>
       <c r="J7" s="5" t="s">
         <v>159</v>
       </c>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="X7" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -3544,9 +3544,15 @@
       <c r="E9" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="F9" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="I9" s="5" t="s">
         <v>159</v>
       </c>
@@ -3594,7 +3600,7 @@
       </c>
       <c r="X9" s="3">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -3768,9 +3774,7 @@
       <c r="H12" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="I12" s="5"/>
       <c r="J12" s="5" t="s">
         <v>159</v>
       </c>
@@ -3815,7 +3819,7 @@
       </c>
       <c r="X12" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -3978,7 +3982,9 @@
         <v>159</v>
       </c>
       <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="F15" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="G15" s="5" t="s">
         <v>159</v>
       </c>
@@ -4030,7 +4036,7 @@
       </c>
       <c r="X15" s="3">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Profesor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFA9E77-6085-4335-A3F7-2279506D6D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5638D4A-7940-48FC-85C6-753F27D4D595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="18000" windowHeight="9270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pruebas_software" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="161">
   <si>
     <t>Nombre</t>
   </si>
@@ -3405,7 +3405,9 @@
       <c r="H7" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="I7" s="5"/>
+      <c r="I7" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="J7" s="5" t="s">
         <v>159</v>
       </c>
@@ -3450,7 +3452,7 @@
       </c>
       <c r="X7" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Profesor\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DOCENTE\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5638D4A-7940-48FC-85C6-753F27D4D595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8507917E-BA4A-4087-982D-95DC071150B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="18000" windowHeight="9270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pruebas_software" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="161">
   <si>
     <t>Nombre</t>
   </si>
@@ -1052,13 +1052,13 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>159</v>
@@ -1119,38 +1119,32 @@
         <v>159</v>
       </c>
       <c r="X2" s="3">
-        <f t="shared" ref="X2:X26" si="0">COUNTBLANK(D2:W2)</f>
+        <f>COUNTBLANK(D2:W2)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="E3" s="6"/>
       <c r="F3" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I3" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="I3" s="6"/>
       <c r="J3" s="6" t="s">
         <v>159</v>
       </c>
@@ -1194,19 +1188,19 @@
         <v>159</v>
       </c>
       <c r="X3" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D3:W3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>159</v>
@@ -1215,7 +1209,9 @@
       <c r="F4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="6"/>
+      <c r="G4" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="H4" s="6" t="s">
         <v>159</v>
       </c>
@@ -1265,19 +1261,19 @@
         <v>159</v>
       </c>
       <c r="X4" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>COUNTBLANK(D4:W4)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>159</v>
@@ -1291,9 +1287,7 @@
       <c r="G5" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="H5" s="6"/>
       <c r="I5" s="6" t="s">
         <v>159</v>
       </c>
@@ -1340,19 +1334,19 @@
         <v>159</v>
       </c>
       <c r="X5" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D5:W5)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>159</v>
@@ -1366,7 +1360,9 @@
       <c r="G6" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H6" s="6"/>
+      <c r="H6" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="I6" s="6" t="s">
         <v>159</v>
       </c>
@@ -1413,19 +1409,19 @@
         <v>159</v>
       </c>
       <c r="X6" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTBLANK(D6:W6)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>159</v>
@@ -1488,19 +1484,19 @@
         <v>159</v>
       </c>
       <c r="X7" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D7:W7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>159</v>
@@ -1563,27 +1559,27 @@
         <v>159</v>
       </c>
       <c r="X8" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D8:W8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="G9" s="6" t="s">
         <v>159</v>
       </c>
@@ -1636,19 +1632,19 @@
         <v>159</v>
       </c>
       <c r="X9" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D9:W9)</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>159</v>
@@ -1659,9 +1655,7 @@
       <c r="F10" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="G10" s="6"/>
       <c r="H10" s="6" t="s">
         <v>159</v>
       </c>
@@ -1711,33 +1705,33 @@
         <v>159</v>
       </c>
       <c r="X10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D10:W10)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E11" s="6"/>
+      <c r="E11" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="F11" s="6" t="s">
         <v>159</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="H11" s="6"/>
       <c r="I11" s="6" t="s">
         <v>159</v>
       </c>
@@ -1784,26 +1778,24 @@
         <v>159</v>
       </c>
       <c r="X11" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D11:W11)</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
         <v>159</v>
       </c>
@@ -1859,19 +1851,19 @@
         <v>159</v>
       </c>
       <c r="X12" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D12:W12)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>159</v>
@@ -1885,7 +1877,9 @@
       <c r="G13" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H13" s="6"/>
+      <c r="H13" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="I13" s="6" t="s">
         <v>159</v>
       </c>
@@ -1932,19 +1926,19 @@
         <v>159</v>
       </c>
       <c r="X13" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTBLANK(D13:W13)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>159</v>
@@ -1959,9 +1953,7 @@
       <c r="H14" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="I14" s="6"/>
       <c r="J14" s="6" t="s">
         <v>159</v>
       </c>
@@ -2005,8 +1997,8 @@
         <v>159</v>
       </c>
       <c r="X14" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTBLANK(D14:W14)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -2078,19 +2070,19 @@
         <v>159</v>
       </c>
       <c r="X15" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D15:W15)</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>159</v>
@@ -2153,26 +2145,24 @@
         <v>159</v>
       </c>
       <c r="X16" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D16:W16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
         <v>159</v>
       </c>
@@ -2182,9 +2172,7 @@
       <c r="H17" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="I17" s="6"/>
       <c r="J17" s="6" t="s">
         <v>159</v>
       </c>
@@ -2228,19 +2216,19 @@
         <v>159</v>
       </c>
       <c r="X17" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D17:W17)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>159</v>
@@ -2303,19 +2291,19 @@
         <v>159</v>
       </c>
       <c r="X18" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D18:W18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>159</v>
@@ -2323,12 +2311,8 @@
       <c r="E19" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
       <c r="H19" s="6" t="s">
         <v>159</v>
       </c>
@@ -2378,24 +2362,26 @@
         <v>159</v>
       </c>
       <c r="X19" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D19:W19)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E20" s="6"/>
+      <c r="E20" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="F20" s="6" t="s">
         <v>159</v>
       </c>
@@ -2451,19 +2437,19 @@
         <v>159</v>
       </c>
       <c r="X20" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTBLANK(D20:W20)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>159</v>
@@ -2474,7 +2460,9 @@
       <c r="F21" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G21" s="6"/>
+      <c r="G21" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="H21" s="6" t="s">
         <v>159</v>
       </c>
@@ -2524,27 +2512,27 @@
         <v>159</v>
       </c>
       <c r="X21" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTBLANK(D21:W21)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="E22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F22" s="6"/>
       <c r="G22" s="6" t="s">
         <v>159</v>
       </c>
@@ -2597,24 +2585,26 @@
         <v>159</v>
       </c>
       <c r="X22" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D22:W22)</f>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E23" s="6"/>
+      <c r="E23" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="F23" s="6" t="s">
         <v>159</v>
       </c>
@@ -2670,19 +2660,19 @@
         <v>159</v>
       </c>
       <c r="X23" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTBLANK(D23:W23)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>159</v>
@@ -2690,8 +2680,12 @@
       <c r="E24" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
+      <c r="F24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="H24" s="6" t="s">
         <v>159</v>
       </c>
@@ -2741,19 +2735,19 @@
         <v>159</v>
       </c>
       <c r="X24" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>COUNTBLANK(D24:W24)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>159</v>
@@ -2770,9 +2764,7 @@
       <c r="H25" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I25" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="I25" s="6"/>
       <c r="J25" s="6" t="s">
         <v>159</v>
       </c>
@@ -2816,8 +2808,8 @@
         <v>159</v>
       </c>
       <c r="X25" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D25:W25)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
@@ -2891,14 +2883,14 @@
         <v>159</v>
       </c>
       <c r="X26" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D26:W26)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:X26" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X26">
-      <sortCondition ref="C1:C26"/>
+      <sortCondition ref="B1:B26"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DOCENTE\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Profesor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8507917E-BA4A-4087-982D-95DC071150B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874E3AE2-16C7-4B37-AB2F-465EC03CD3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pruebas_software" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="164">
   <si>
     <t>Nombre</t>
   </si>
@@ -521,6 +521,15 @@
   </si>
   <si>
     <t>total_fallas</t>
+  </si>
+  <si>
+    <t>jeison</t>
+  </si>
+  <si>
+    <t>caraballo</t>
+  </si>
+  <si>
+    <t>matricula tardia</t>
   </si>
 </sst>
 </file>
@@ -571,7 +580,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -594,12 +603,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
@@ -614,6 +660,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1119,7 +1175,7 @@
         <v>159</v>
       </c>
       <c r="X2" s="3">
-        <f>COUNTBLANK(D2:W2)</f>
+        <f t="shared" ref="X2:X26" si="0">COUNTBLANK(D2:W2)</f>
         <v>1</v>
       </c>
     </row>
@@ -1188,7 +1244,7 @@
         <v>159</v>
       </c>
       <c r="X3" s="3">
-        <f>COUNTBLANK(D3:W3)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -1261,7 +1317,7 @@
         <v>159</v>
       </c>
       <c r="X4" s="3">
-        <f>COUNTBLANK(D4:W4)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1334,7 +1390,7 @@
         <v>159</v>
       </c>
       <c r="X5" s="3">
-        <f>COUNTBLANK(D5:W5)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1409,7 +1465,7 @@
         <v>159</v>
       </c>
       <c r="X6" s="3">
-        <f>COUNTBLANK(D6:W6)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1484,7 +1540,7 @@
         <v>159</v>
       </c>
       <c r="X7" s="3">
-        <f>COUNTBLANK(D7:W7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1559,7 +1615,7 @@
         <v>159</v>
       </c>
       <c r="X8" s="3">
-        <f>COUNTBLANK(D8:W8)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1632,7 +1688,7 @@
         <v>159</v>
       </c>
       <c r="X9" s="3">
-        <f>COUNTBLANK(D9:W9)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1705,7 +1761,7 @@
         <v>159</v>
       </c>
       <c r="X10" s="3">
-        <f>COUNTBLANK(D10:W10)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1778,7 +1834,7 @@
         <v>159</v>
       </c>
       <c r="X11" s="3">
-        <f>COUNTBLANK(D11:W11)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1851,7 +1907,7 @@
         <v>159</v>
       </c>
       <c r="X12" s="3">
-        <f>COUNTBLANK(D12:W12)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1926,7 +1982,7 @@
         <v>159</v>
       </c>
       <c r="X13" s="3">
-        <f>COUNTBLANK(D13:W13)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1997,7 +2053,7 @@
         <v>159</v>
       </c>
       <c r="X14" s="3">
-        <f>COUNTBLANK(D14:W14)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2070,7 +2126,7 @@
         <v>159</v>
       </c>
       <c r="X15" s="3">
-        <f>COUNTBLANK(D15:W15)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2145,7 +2201,7 @@
         <v>159</v>
       </c>
       <c r="X16" s="3">
-        <f>COUNTBLANK(D16:W16)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2216,7 +2272,7 @@
         <v>159</v>
       </c>
       <c r="X17" s="3">
-        <f>COUNTBLANK(D17:W17)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2291,7 +2347,7 @@
         <v>159</v>
       </c>
       <c r="X18" s="3">
-        <f>COUNTBLANK(D18:W18)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2362,7 +2418,7 @@
         <v>159</v>
       </c>
       <c r="X19" s="3">
-        <f>COUNTBLANK(D19:W19)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2437,7 +2493,7 @@
         <v>159</v>
       </c>
       <c r="X20" s="3">
-        <f>COUNTBLANK(D20:W20)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2512,7 +2568,7 @@
         <v>159</v>
       </c>
       <c r="X21" s="3">
-        <f>COUNTBLANK(D21:W21)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2585,7 +2641,7 @@
         <v>159</v>
       </c>
       <c r="X22" s="3">
-        <f>COUNTBLANK(D22:W22)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2660,7 +2716,7 @@
         <v>159</v>
       </c>
       <c r="X23" s="3">
-        <f>COUNTBLANK(D23:W23)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2735,7 +2791,7 @@
         <v>159</v>
       </c>
       <c r="X24" s="3">
-        <f>COUNTBLANK(D24:W24)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2808,7 +2864,7 @@
         <v>159</v>
       </c>
       <c r="X25" s="3">
-        <f>COUNTBLANK(D25:W25)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2883,7 +2939,7 @@
         <v>159</v>
       </c>
       <c r="X26" s="3">
-        <f>COUNTBLANK(D26:W26)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2915,7 +2971,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC8DBC52-987A-4412-B43F-A9A2EA19A4E3}">
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.375" bestFit="1" customWidth="1"/>
@@ -3101,9 +3157,7 @@
       <c r="I3" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="J3" s="5"/>
       <c r="K3" s="5" t="s">
         <v>159</v>
       </c>
@@ -3145,7 +3199,7 @@
       </c>
       <c r="X3" s="3">
         <f t="shared" ref="X3:X22" si="0">COUNTBLANK(D3:W3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" s="7"/>
     </row>
@@ -3412,7 +3466,7 @@
       <c r="M7" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="N7" s="5" t="s">
+      <c r="N7" s="11" t="s">
         <v>159</v>
       </c>
       <c r="O7" s="5" t="s">
@@ -3760,8 +3814,12 @@
       <c r="D12" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="E12" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="G12" s="5" t="s">
         <v>159</v>
       </c>
@@ -3813,7 +3871,7 @@
       </c>
       <c r="X12" s="3">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -4554,13 +4612,81 @@
         <v>0</v>
       </c>
     </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="O23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="P23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="R23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="S23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="T23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="U23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="V23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="W23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="X23" s="3">
+        <f>COUNTBLANK(I23:W23)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:W1" xr:uid="{AC8DBC52-987A-4412-B43F-A9A2EA19A4E3}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W22">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W23">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="D2:W22">
+  <mergeCells count="1">
+    <mergeCell ref="D23:H23"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D2:W22 D23 I23:W23">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"x"</formula>
     </cfRule>
@@ -4576,5 +4702,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Profesor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874E3AE2-16C7-4B37-AB2F-465EC03CD3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E9CDA06-BF4E-4BCD-987D-7AA71BCD1CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="164">
   <si>
     <t>Nombre</t>
   </si>
@@ -660,6 +660,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -669,7 +670,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3466,7 +3466,7 @@
       <c r="M7" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="N7" s="8" t="s">
         <v>159</v>
       </c>
       <c r="O7" s="5" t="s">
@@ -3535,9 +3535,7 @@
       <c r="K8" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L8" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="L8" s="5"/>
       <c r="M8" s="5" t="s">
         <v>159</v>
       </c>
@@ -3573,7 +3571,7 @@
       </c>
       <c r="X8" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -4423,9 +4421,7 @@
       <c r="K20" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L20" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="L20" s="5"/>
       <c r="M20" s="5" t="s">
         <v>159</v>
       </c>
@@ -4461,7 +4457,7 @@
       </c>
       <c r="X20" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
@@ -4496,9 +4492,7 @@
       <c r="K21" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L21" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="L21" s="5"/>
       <c r="M21" s="5" t="s">
         <v>159</v>
       </c>
@@ -4534,7 +4528,7 @@
       </c>
       <c r="X21" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
@@ -4620,13 +4614,13 @@
       <c r="C23" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="11"/>
       <c r="I23" s="5" t="s">
         <v>159</v>
       </c>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Profesor\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DOCENTE\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E9CDA06-BF4E-4BCD-987D-7AA71BCD1CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93442131-7FE9-49CA-A30A-2C66B71AA2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pruebas_software" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="164">
   <si>
     <t>Nombre</t>
   </si>
@@ -1108,13 +1108,13 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>159</v>
@@ -1175,32 +1175,38 @@
         <v>159</v>
       </c>
       <c r="X2" s="3">
-        <f t="shared" ref="X2:X26" si="0">COUNTBLANK(D2:W2)</f>
+        <f>COUNTBLANK(D2:W2)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="F3" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G3" s="6"/>
+      <c r="G3" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="H3" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I3" s="6"/>
+      <c r="I3" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="J3" s="6" t="s">
         <v>159</v>
       </c>
@@ -1244,19 +1250,19 @@
         <v>159</v>
       </c>
       <c r="X3" s="3">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>COUNTBLANK(D3:W3)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>159</v>
@@ -1265,15 +1271,11 @@
       <c r="F4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="G4" s="6"/>
       <c r="H4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="I4" s="6"/>
       <c r="J4" s="6" t="s">
         <v>159</v>
       </c>
@@ -1317,19 +1319,19 @@
         <v>159</v>
       </c>
       <c r="X4" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTBLANK(D4:W4)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>159</v>
@@ -1343,7 +1345,9 @@
       <c r="G5" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H5" s="6"/>
+      <c r="H5" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="I5" s="6" t="s">
         <v>159</v>
       </c>
@@ -1390,19 +1394,19 @@
         <v>159</v>
       </c>
       <c r="X5" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTBLANK(D5:W5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>159</v>
@@ -1416,9 +1420,7 @@
       <c r="G6" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="H6" s="6"/>
       <c r="I6" s="6" t="s">
         <v>159</v>
       </c>
@@ -1465,19 +1467,19 @@
         <v>159</v>
       </c>
       <c r="X6" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D6:W6)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>159</v>
@@ -1540,19 +1542,19 @@
         <v>159</v>
       </c>
       <c r="X7" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D7:W7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>159</v>
@@ -1615,27 +1617,27 @@
         <v>159</v>
       </c>
       <c r="X8" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D8:W8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="E9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F9" s="6"/>
       <c r="G9" s="6" t="s">
         <v>159</v>
       </c>
@@ -1688,19 +1690,19 @@
         <v>159</v>
       </c>
       <c r="X9" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D9:W9)</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>159</v>
@@ -1711,7 +1713,9 @@
       <c r="F10" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G10" s="6"/>
+      <c r="G10" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="H10" s="6" t="s">
         <v>159</v>
       </c>
@@ -1724,9 +1728,7 @@
       <c r="K10" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="L10" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="L10" s="6"/>
       <c r="M10" s="6" t="s">
         <v>159</v>
       </c>
@@ -1761,33 +1763,33 @@
         <v>159</v>
       </c>
       <c r="X10" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D10:W10)</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
         <v>159</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H11" s="6"/>
+      <c r="H11" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="I11" s="6" t="s">
         <v>159</v>
       </c>
@@ -1834,24 +1836,26 @@
         <v>159</v>
       </c>
       <c r="X11" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D11:W11)</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E12" s="6"/>
+      <c r="E12" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="F12" s="6" t="s">
         <v>159</v>
       </c>
@@ -1907,19 +1911,19 @@
         <v>159</v>
       </c>
       <c r="X12" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTBLANK(D12:W12)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>159</v>
@@ -1933,9 +1937,7 @@
       <c r="G13" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="H13" s="6"/>
       <c r="I13" s="6" t="s">
         <v>159</v>
       </c>
@@ -1982,19 +1984,19 @@
         <v>159</v>
       </c>
       <c r="X13" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D13:W13)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>159</v>
@@ -2009,7 +2011,9 @@
       <c r="H14" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I14" s="6"/>
+      <c r="I14" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="J14" s="6" t="s">
         <v>159</v>
       </c>
@@ -2053,8 +2057,8 @@
         <v>159</v>
       </c>
       <c r="X14" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>COUNTBLANK(D14:W14)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -2126,19 +2130,19 @@
         <v>159</v>
       </c>
       <c r="X15" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D15:W15)</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>159</v>
@@ -2201,24 +2205,26 @@
         <v>159</v>
       </c>
       <c r="X16" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D16:W16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E17" s="6"/>
+      <c r="E17" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="F17" s="6" t="s">
         <v>159</v>
       </c>
@@ -2228,7 +2234,9 @@
       <c r="H17" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I17" s="6"/>
+      <c r="I17" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="J17" s="6" t="s">
         <v>159</v>
       </c>
@@ -2272,19 +2280,19 @@
         <v>159</v>
       </c>
       <c r="X17" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>COUNTBLANK(D17:W17)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>159</v>
@@ -2301,9 +2309,7 @@
       <c r="H18" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="I18" s="6"/>
       <c r="J18" s="6" t="s">
         <v>159</v>
       </c>
@@ -2347,19 +2353,19 @@
         <v>159</v>
       </c>
       <c r="X18" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D18:W18)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>159</v>
@@ -2367,8 +2373,12 @@
       <c r="E19" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
+      <c r="F19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="H19" s="6" t="s">
         <v>159</v>
       </c>
@@ -2418,26 +2428,24 @@
         <v>159</v>
       </c>
       <c r="X19" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>COUNTBLANK(D19:W19)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="E20" s="6"/>
       <c r="F20" s="6" t="s">
         <v>159</v>
       </c>
@@ -2493,19 +2501,19 @@
         <v>159</v>
       </c>
       <c r="X20" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D20:W20)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>159</v>
@@ -2516,9 +2524,7 @@
       <c r="F21" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G21" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="G21" s="6"/>
       <c r="H21" s="6" t="s">
         <v>159</v>
       </c>
@@ -2568,36 +2574,34 @@
         <v>159</v>
       </c>
       <c r="X21" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D21:W21)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="G22" s="6" t="s">
         <v>159</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I22" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="I22" s="6"/>
       <c r="J22" s="6" t="s">
         <v>159</v>
       </c>
@@ -2641,26 +2645,24 @@
         <v>159</v>
       </c>
       <c r="X22" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTBLANK(D22:W22)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="E23" s="6"/>
       <c r="F23" s="6" t="s">
         <v>159</v>
       </c>
@@ -2670,9 +2672,7 @@
       <c r="H23" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I23" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="I23" s="6"/>
       <c r="J23" s="6" t="s">
         <v>159</v>
       </c>
@@ -2716,19 +2716,19 @@
         <v>159</v>
       </c>
       <c r="X23" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D23:W23)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>159</v>
@@ -2736,12 +2736,8 @@
       <c r="E24" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
       <c r="H24" s="6" t="s">
         <v>159</v>
       </c>
@@ -2791,19 +2787,19 @@
         <v>159</v>
       </c>
       <c r="X24" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D24:W24)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>159</v>
@@ -2820,7 +2816,9 @@
       <c r="H25" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I25" s="6"/>
+      <c r="I25" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="J25" s="6" t="s">
         <v>159</v>
       </c>
@@ -2864,8 +2862,8 @@
         <v>159</v>
       </c>
       <c r="X25" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTBLANK(D25:W25)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
@@ -2902,9 +2900,7 @@
       <c r="K26" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="L26" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="L26" s="6"/>
       <c r="M26" s="6" t="s">
         <v>159</v>
       </c>
@@ -2939,14 +2935,14 @@
         <v>159</v>
       </c>
       <c r="X26" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D26:W26)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:X26" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X26">
-      <sortCondition ref="B1:B26"/>
+      <sortCondition ref="C1:C26"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DOCENTE\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Profesor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93442131-7FE9-49CA-A30A-2C66B71AA2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322BCBF7-6E9E-43EB-9ACD-046D8FD7FFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pruebas_software" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="165">
   <si>
     <t>Nombre</t>
   </si>
@@ -530,6 +530,9 @@
   </si>
   <si>
     <t>matricula tardia</t>
+  </si>
+  <si>
+    <t>X</t>
   </si>
 </sst>
 </file>
@@ -572,12 +575,30 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -645,7 +666,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
@@ -670,6 +691,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1108,13 +1133,13 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>70</v>
+        <v>77</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>76</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>159</v>
@@ -1144,9 +1169,7 @@
       <c r="M2" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N2" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N2" s="6"/>
       <c r="O2" s="6" t="s">
         <v>159</v>
       </c>
@@ -1176,37 +1199,31 @@
       </c>
       <c r="X2" s="3">
         <f>COUNTBLANK(D2:W2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="E3" s="6"/>
       <c r="F3" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I3" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="I3" s="6"/>
       <c r="J3" s="6" t="s">
         <v>159</v>
       </c>
@@ -1219,9 +1236,7 @@
       <c r="M3" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N3" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N3" s="6"/>
       <c r="O3" s="6" t="s">
         <v>159</v>
       </c>
@@ -1251,18 +1266,18 @@
       </c>
       <c r="X3" s="3">
         <f>COUNTBLANK(D3:W3)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>159</v>
@@ -1271,11 +1286,15 @@
       <c r="F4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="6"/>
+      <c r="G4" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="H4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I4" s="6"/>
+      <c r="I4" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="J4" s="6" t="s">
         <v>159</v>
       </c>
@@ -1288,9 +1307,7 @@
       <c r="M4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N4" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N4" s="6"/>
       <c r="O4" s="6" t="s">
         <v>159</v>
       </c>
@@ -1320,18 +1337,18 @@
       </c>
       <c r="X4" s="3">
         <f>COUNTBLANK(D4:W4)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>16</v>
+        <v>74</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>159</v>
@@ -1345,9 +1362,7 @@
       <c r="G5" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="H5" s="6"/>
       <c r="I5" s="6" t="s">
         <v>159</v>
       </c>
@@ -1363,9 +1378,7 @@
       <c r="M5" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N5" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N5" s="6"/>
       <c r="O5" s="6" t="s">
         <v>159</v>
       </c>
@@ -1395,18 +1408,18 @@
       </c>
       <c r="X5" s="3">
         <f>COUNTBLANK(D5:W5)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>159</v>
@@ -1420,7 +1433,9 @@
       <c r="G6" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H6" s="6"/>
+      <c r="H6" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="I6" s="6" t="s">
         <v>159</v>
       </c>
@@ -1436,9 +1451,7 @@
       <c r="M6" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N6" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N6" s="6"/>
       <c r="O6" s="6" t="s">
         <v>159</v>
       </c>
@@ -1473,13 +1486,13 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>159</v>
@@ -1511,9 +1524,7 @@
       <c r="M7" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N7" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N7" s="6"/>
       <c r="O7" s="6" t="s">
         <v>159</v>
       </c>
@@ -1543,18 +1554,18 @@
       </c>
       <c r="X7" s="3">
         <f>COUNTBLANK(D7:W7)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>159</v>
@@ -1580,15 +1591,11 @@
       <c r="K8" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="L8" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="L8" s="6"/>
       <c r="M8" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N8" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N8" s="6"/>
       <c r="O8" s="6" t="s">
         <v>159</v>
       </c>
@@ -1618,26 +1625,26 @@
       </c>
       <c r="X8" s="3">
         <f>COUNTBLANK(D8:W8)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="G9" s="6" t="s">
         <v>159</v>
       </c>
@@ -1659,9 +1666,7 @@
       <c r="M9" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N9" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N9" s="6"/>
       <c r="O9" s="6" t="s">
         <v>159</v>
       </c>
@@ -1691,18 +1696,18 @@
       </c>
       <c r="X9" s="3">
         <f>COUNTBLANK(D9:W9)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>159</v>
@@ -1713,9 +1718,7 @@
       <c r="F10" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="G10" s="6"/>
       <c r="H10" s="6" t="s">
         <v>159</v>
       </c>
@@ -1728,13 +1731,13 @@
       <c r="K10" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="L10" s="6"/>
+      <c r="L10" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="M10" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N10" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N10" s="6"/>
       <c r="O10" s="6" t="s">
         <v>159</v>
       </c>
@@ -1764,32 +1767,32 @@
       </c>
       <c r="X10" s="3">
         <f>COUNTBLANK(D10:W10)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E11" s="6"/>
+      <c r="E11" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="F11" s="6" t="s">
         <v>159</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="H11" s="6"/>
       <c r="I11" s="6" t="s">
         <v>159</v>
       </c>
@@ -1805,9 +1808,7 @@
       <c r="M11" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N11" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N11" s="6"/>
       <c r="O11" s="6" t="s">
         <v>159</v>
       </c>
@@ -1837,25 +1838,23 @@
       </c>
       <c r="X11" s="3">
         <f>COUNTBLANK(D11:W11)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
         <v>159</v>
       </c>
@@ -1880,9 +1879,7 @@
       <c r="M12" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N12" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N12" s="6"/>
       <c r="O12" s="6" t="s">
         <v>159</v>
       </c>
@@ -1912,18 +1909,18 @@
       </c>
       <c r="X12" s="3">
         <f>COUNTBLANK(D12:W12)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>159</v>
@@ -1937,7 +1934,9 @@
       <c r="G13" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H13" s="6"/>
+      <c r="H13" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="I13" s="6" t="s">
         <v>159</v>
       </c>
@@ -1953,9 +1952,7 @@
       <c r="M13" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N13" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N13" s="6"/>
       <c r="O13" s="6" t="s">
         <v>159</v>
       </c>
@@ -1990,13 +1987,13 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>159</v>
@@ -2011,9 +2008,7 @@
       <c r="H14" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="I14" s="6"/>
       <c r="J14" s="6" t="s">
         <v>159</v>
       </c>
@@ -2026,9 +2021,7 @@
       <c r="M14" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N14" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N14" s="6"/>
       <c r="O14" s="6" t="s">
         <v>159</v>
       </c>
@@ -2058,17 +2051,17 @@
       </c>
       <c r="X14" s="3">
         <f>COUNTBLANK(D14:W14)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="13" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -2099,9 +2092,7 @@
       <c r="M15" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N15" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N15" s="6"/>
       <c r="O15" s="6" t="s">
         <v>159</v>
       </c>
@@ -2131,18 +2122,18 @@
       </c>
       <c r="X15" s="3">
         <f>COUNTBLANK(D15:W15)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>159</v>
@@ -2174,9 +2165,7 @@
       <c r="M16" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N16" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N16" s="6"/>
       <c r="O16" s="6" t="s">
         <v>159</v>
       </c>
@@ -2206,25 +2195,23 @@
       </c>
       <c r="X16" s="3">
         <f>COUNTBLANK(D16:W16)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
         <v>159</v>
       </c>
@@ -2234,9 +2221,7 @@
       <c r="H17" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="I17" s="6"/>
       <c r="J17" s="6" t="s">
         <v>159</v>
       </c>
@@ -2249,9 +2234,7 @@
       <c r="M17" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N17" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N17" s="6"/>
       <c r="O17" s="6" t="s">
         <v>159</v>
       </c>
@@ -2281,18 +2264,18 @@
       </c>
       <c r="X17" s="3">
         <f>COUNTBLANK(D17:W17)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>28</v>
+        <v>14</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>159</v>
@@ -2309,7 +2292,9 @@
       <c r="H18" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I18" s="6"/>
+      <c r="I18" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="J18" s="6" t="s">
         <v>159</v>
       </c>
@@ -2322,9 +2307,7 @@
       <c r="M18" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N18" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N18" s="6"/>
       <c r="O18" s="6" t="s">
         <v>159</v>
       </c>
@@ -2359,13 +2342,13 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>159</v>
@@ -2373,12 +2356,8 @@
       <c r="E19" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
       <c r="H19" s="6" t="s">
         <v>159</v>
       </c>
@@ -2397,9 +2376,7 @@
       <c r="M19" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N19" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N19" s="6"/>
       <c r="O19" s="6" t="s">
         <v>159</v>
       </c>
@@ -2429,23 +2406,25 @@
       </c>
       <c r="X19" s="3">
         <f>COUNTBLANK(D19:W19)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E20" s="6"/>
+      <c r="E20" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="F20" s="6" t="s">
         <v>159</v>
       </c>
@@ -2470,9 +2449,7 @@
       <c r="M20" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N20" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N20" s="6"/>
       <c r="O20" s="6" t="s">
         <v>159</v>
       </c>
@@ -2507,13 +2484,13 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>159</v>
@@ -2524,7 +2501,9 @@
       <c r="F21" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G21" s="6"/>
+      <c r="G21" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="H21" s="6" t="s">
         <v>159</v>
       </c>
@@ -2543,9 +2522,7 @@
       <c r="M21" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N21" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N21" s="6"/>
       <c r="O21" s="6" t="s">
         <v>159</v>
       </c>
@@ -2580,28 +2557,30 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="E22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F22" s="6"/>
       <c r="G22" s="6" t="s">
         <v>159</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I22" s="6"/>
+      <c r="I22" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="J22" s="6" t="s">
         <v>159</v>
       </c>
@@ -2614,9 +2593,7 @@
       <c r="M22" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N22" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N22" s="6"/>
       <c r="O22" s="6" t="s">
         <v>159</v>
       </c>
@@ -2651,18 +2628,20 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E23" s="6"/>
+      <c r="E23" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="F23" s="6" t="s">
         <v>159</v>
       </c>
@@ -2672,7 +2651,9 @@
       <c r="H23" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I23" s="6"/>
+      <c r="I23" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="J23" s="6" t="s">
         <v>159</v>
       </c>
@@ -2685,9 +2666,7 @@
       <c r="M23" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N23" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N23" s="6"/>
       <c r="O23" s="6" t="s">
         <v>159</v>
       </c>
@@ -2717,18 +2696,18 @@
       </c>
       <c r="X23" s="3">
         <f>COUNTBLANK(D23:W23)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>159</v>
@@ -2736,8 +2715,12 @@
       <c r="E24" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
+      <c r="F24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="H24" s="6" t="s">
         <v>159</v>
       </c>
@@ -2756,9 +2739,7 @@
       <c r="M24" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N24" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N24" s="6"/>
       <c r="O24" s="6" t="s">
         <v>159</v>
       </c>
@@ -2788,18 +2769,18 @@
       </c>
       <c r="X24" s="3">
         <f>COUNTBLANK(D24:W24)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>159</v>
@@ -2816,9 +2797,7 @@
       <c r="H25" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I25" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="I25" s="6"/>
       <c r="J25" s="6" t="s">
         <v>159</v>
       </c>
@@ -2831,9 +2810,7 @@
       <c r="M25" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N25" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N25" s="6"/>
       <c r="O25" s="6" t="s">
         <v>159</v>
       </c>
@@ -2863,17 +2840,17 @@
       </c>
       <c r="X25" s="3">
         <f>COUNTBLANK(D25:W25)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D26" s="6" t="s">
@@ -2904,9 +2881,7 @@
       <c r="M26" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N26" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="N26" s="6"/>
       <c r="O26" s="6" t="s">
         <v>159</v>
       </c>
@@ -2936,13 +2911,13 @@
       </c>
       <c r="X26" s="3">
         <f>COUNTBLANK(D26:W26)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:X26" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X26">
-      <sortCondition ref="C1:C26"/>
+      <sortCondition ref="B1:B26"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -3129,10 +3104,10 @@
       <c r="A3" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="12" t="s">
         <v>150</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -3163,9 +3138,7 @@
       <c r="M3" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="N3" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="N3" s="5"/>
       <c r="O3" s="5" t="s">
         <v>159</v>
       </c>
@@ -3195,7 +3168,7 @@
       </c>
       <c r="X3" s="3">
         <f t="shared" ref="X3:X22" si="0">COUNTBLANK(D3:W3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z3" s="7"/>
     </row>
@@ -3203,10 +3176,10 @@
       <c r="A4" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="14" t="s">
         <v>142</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -3426,10 +3399,10 @@
       <c r="A7" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="14" t="s">
         <v>119</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -3462,9 +3435,7 @@
       <c r="M7" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="N7" s="8" t="s">
-        <v>159</v>
-      </c>
+      <c r="N7" s="8"/>
       <c r="O7" s="5" t="s">
         <v>159</v>
       </c>
@@ -3494,7 +3465,7 @@
       </c>
       <c r="X7" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -3799,10 +3770,10 @@
       <c r="A12" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="12" t="s">
         <v>116</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -4164,10 +4135,10 @@
       <c r="A17" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="14" t="s">
         <v>125</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -4239,10 +4210,10 @@
       <c r="A18" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="15" t="s">
         <v>133</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -4312,10 +4283,10 @@
       <c r="A19" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="12" t="s">
         <v>139</v>
       </c>
       <c r="D19" s="5" t="s">
@@ -4349,7 +4320,7 @@
         <v>159</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="O19" s="5" t="s">
         <v>159</v>
@@ -4460,10 +4431,10 @@
       <c r="A21" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="12" t="s">
         <v>113</v>
       </c>
       <c r="D21" s="5" t="s">

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Profesor\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DOCENTE\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322BCBF7-6E9E-43EB-9ACD-046D8FD7FFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D4DFAC-BF44-4B86-9D8B-BEA77152AB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pruebas_software" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="165">
   <si>
     <t>Nombre</t>
   </si>
@@ -682,6 +682,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -691,10 +695,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1133,13 +1133,13 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>76</v>
+        <v>71</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>159</v>
@@ -1169,7 +1169,9 @@
       <c r="M2" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N2" s="6"/>
+      <c r="N2" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O2" s="6" t="s">
         <v>159</v>
       </c>
@@ -1199,31 +1201,37 @@
       </c>
       <c r="X2" s="3">
         <f>COUNTBLANK(D2:W2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>40</v>
+        <v>14</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>13</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="F3" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G3" s="6"/>
+      <c r="G3" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="H3" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I3" s="6"/>
+      <c r="I3" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="J3" s="6" t="s">
         <v>159</v>
       </c>
@@ -1236,7 +1244,9 @@
       <c r="M3" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N3" s="6"/>
+      <c r="N3" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O3" s="6" t="s">
         <v>159</v>
       </c>
@@ -1266,18 +1276,18 @@
       </c>
       <c r="X3" s="3">
         <f>COUNTBLANK(D3:W3)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>159</v>
@@ -1286,15 +1296,11 @@
       <c r="F4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="G4" s="6"/>
       <c r="H4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="I4" s="6"/>
       <c r="J4" s="6" t="s">
         <v>159</v>
       </c>
@@ -1307,7 +1313,9 @@
       <c r="M4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N4" s="6"/>
+      <c r="N4" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O4" s="6" t="s">
         <v>159</v>
       </c>
@@ -1337,18 +1345,18 @@
       </c>
       <c r="X4" s="3">
         <f>COUNTBLANK(D4:W4)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>73</v>
+        <v>17</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>159</v>
@@ -1362,7 +1370,9 @@
       <c r="G5" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H5" s="6"/>
+      <c r="H5" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="I5" s="6" t="s">
         <v>159</v>
       </c>
@@ -1378,7 +1388,9 @@
       <c r="M5" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N5" s="6"/>
+      <c r="N5" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O5" s="6" t="s">
         <v>159</v>
       </c>
@@ -1408,18 +1420,18 @@
       </c>
       <c r="X5" s="3">
         <f>COUNTBLANK(D5:W5)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
+        <v>74</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>73</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>159</v>
@@ -1433,9 +1445,7 @@
       <c r="G6" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="H6" s="6"/>
       <c r="I6" s="6" t="s">
         <v>159</v>
       </c>
@@ -1451,7 +1461,9 @@
       <c r="M6" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N6" s="6"/>
+      <c r="N6" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O6" s="6" t="s">
         <v>159</v>
       </c>
@@ -1486,13 +1498,13 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>159</v>
@@ -1524,7 +1536,9 @@
       <c r="M7" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N7" s="6"/>
+      <c r="N7" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O7" s="6" t="s">
         <v>159</v>
       </c>
@@ -1554,18 +1568,18 @@
       </c>
       <c r="X7" s="3">
         <f>COUNTBLANK(D7:W7)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>159</v>
@@ -1591,11 +1605,15 @@
       <c r="K8" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="L8" s="6"/>
+      <c r="L8" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="M8" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N8" s="6"/>
+      <c r="N8" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O8" s="6" t="s">
         <v>159</v>
       </c>
@@ -1625,26 +1643,26 @@
       </c>
       <c r="X8" s="3">
         <f>COUNTBLANK(D8:W8)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="E9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F9" s="6"/>
       <c r="G9" s="6" t="s">
         <v>159</v>
       </c>
@@ -1666,7 +1684,9 @@
       <c r="M9" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N9" s="6"/>
+      <c r="N9" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O9" s="6" t="s">
         <v>159</v>
       </c>
@@ -1696,18 +1716,18 @@
       </c>
       <c r="X9" s="3">
         <f>COUNTBLANK(D9:W9)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>159</v>
@@ -1718,7 +1738,9 @@
       <c r="F10" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G10" s="6"/>
+      <c r="G10" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="H10" s="6" t="s">
         <v>159</v>
       </c>
@@ -1731,13 +1753,13 @@
       <c r="K10" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="L10" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="L10" s="6"/>
       <c r="M10" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N10" s="6"/>
+      <c r="N10" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O10" s="6" t="s">
         <v>159</v>
       </c>
@@ -1767,32 +1789,32 @@
       </c>
       <c r="X10" s="3">
         <f>COUNTBLANK(D10:W10)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
         <v>159</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H11" s="6"/>
+      <c r="H11" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="I11" s="6" t="s">
         <v>159</v>
       </c>
@@ -1808,7 +1830,9 @@
       <c r="M11" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N11" s="6"/>
+      <c r="N11" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O11" s="6" t="s">
         <v>159</v>
       </c>
@@ -1838,23 +1862,25 @@
       </c>
       <c r="X11" s="3">
         <f>COUNTBLANK(D11:W11)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E12" s="6"/>
+      <c r="E12" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="F12" s="6" t="s">
         <v>159</v>
       </c>
@@ -1879,7 +1905,9 @@
       <c r="M12" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N12" s="6"/>
+      <c r="N12" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O12" s="6" t="s">
         <v>159</v>
       </c>
@@ -1909,18 +1937,18 @@
       </c>
       <c r="X12" s="3">
         <f>COUNTBLANK(D12:W12)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>43</v>
+        <v>77</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>159</v>
@@ -1934,9 +1962,7 @@
       <c r="G13" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="H13" s="6"/>
       <c r="I13" s="6" t="s">
         <v>159</v>
       </c>
@@ -1952,7 +1978,9 @@
       <c r="M13" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N13" s="6"/>
+      <c r="N13" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O13" s="6" t="s">
         <v>159</v>
       </c>
@@ -1987,13 +2015,13 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>159</v>
@@ -2008,7 +2036,9 @@
       <c r="H14" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I14" s="6"/>
+      <c r="I14" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="J14" s="6" t="s">
         <v>159</v>
       </c>
@@ -2021,7 +2051,9 @@
       <c r="M14" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N14" s="6"/>
+      <c r="N14" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O14" s="6" t="s">
         <v>159</v>
       </c>
@@ -2051,17 +2083,17 @@
       </c>
       <c r="X14" s="3">
         <f>COUNTBLANK(D14:W14)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="10" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -2092,7 +2124,9 @@
       <c r="M15" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N15" s="6"/>
+      <c r="N15" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O15" s="6" t="s">
         <v>159</v>
       </c>
@@ -2122,18 +2156,18 @@
       </c>
       <c r="X15" s="3">
         <f>COUNTBLANK(D15:W15)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>159</v>
@@ -2165,7 +2199,9 @@
       <c r="M16" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N16" s="6"/>
+      <c r="N16" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O16" s="6" t="s">
         <v>159</v>
       </c>
@@ -2195,23 +2231,25 @@
       </c>
       <c r="X16" s="3">
         <f>COUNTBLANK(D16:W16)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E17" s="6"/>
+      <c r="E17" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="F17" s="6" t="s">
         <v>159</v>
       </c>
@@ -2221,7 +2259,9 @@
       <c r="H17" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I17" s="6"/>
+      <c r="I17" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="J17" s="6" t="s">
         <v>159</v>
       </c>
@@ -2234,7 +2274,9 @@
       <c r="M17" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N17" s="6"/>
+      <c r="N17" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O17" s="6" t="s">
         <v>159</v>
       </c>
@@ -2264,18 +2306,18 @@
       </c>
       <c r="X17" s="3">
         <f>COUNTBLANK(D17:W17)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>159</v>
@@ -2292,9 +2334,7 @@
       <c r="H18" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="I18" s="6"/>
       <c r="J18" s="6" t="s">
         <v>159</v>
       </c>
@@ -2307,7 +2347,9 @@
       <c r="M18" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N18" s="6"/>
+      <c r="N18" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O18" s="6" t="s">
         <v>159</v>
       </c>
@@ -2342,13 +2384,13 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>159</v>
@@ -2356,8 +2398,12 @@
       <c r="E19" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
+      <c r="F19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="H19" s="6" t="s">
         <v>159</v>
       </c>
@@ -2376,7 +2422,9 @@
       <c r="M19" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N19" s="6"/>
+      <c r="N19" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O19" s="6" t="s">
         <v>159</v>
       </c>
@@ -2406,25 +2454,23 @@
       </c>
       <c r="X19" s="3">
         <f>COUNTBLANK(D19:W19)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="E20" s="6"/>
       <c r="F20" s="6" t="s">
         <v>159</v>
       </c>
@@ -2449,7 +2495,9 @@
       <c r="M20" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N20" s="6"/>
+      <c r="N20" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O20" s="6" t="s">
         <v>159</v>
       </c>
@@ -2484,13 +2532,13 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>159</v>
@@ -2501,9 +2549,7 @@
       <c r="F21" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G21" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="G21" s="6"/>
       <c r="H21" s="6" t="s">
         <v>159</v>
       </c>
@@ -2522,7 +2568,9 @@
       <c r="M21" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N21" s="6"/>
+      <c r="N21" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O21" s="6" t="s">
         <v>159</v>
       </c>
@@ -2557,30 +2605,28 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="G22" s="6" t="s">
         <v>159</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I22" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="I22" s="6"/>
       <c r="J22" s="6" t="s">
         <v>159</v>
       </c>
@@ -2593,7 +2639,9 @@
       <c r="M22" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N22" s="6"/>
+      <c r="N22" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O22" s="6" t="s">
         <v>159</v>
       </c>
@@ -2628,20 +2676,18 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="E23" s="6"/>
       <c r="F23" s="6" t="s">
         <v>159</v>
       </c>
@@ -2651,9 +2697,7 @@
       <c r="H23" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I23" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="I23" s="6"/>
       <c r="J23" s="6" t="s">
         <v>159</v>
       </c>
@@ -2666,7 +2710,9 @@
       <c r="M23" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N23" s="6"/>
+      <c r="N23" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O23" s="6" t="s">
         <v>159</v>
       </c>
@@ -2696,18 +2742,18 @@
       </c>
       <c r="X23" s="3">
         <f>COUNTBLANK(D23:W23)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>159</v>
@@ -2715,12 +2761,8 @@
       <c r="E24" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
       <c r="H24" s="6" t="s">
         <v>159</v>
       </c>
@@ -2739,7 +2781,9 @@
       <c r="M24" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N24" s="6"/>
+      <c r="N24" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O24" s="6" t="s">
         <v>159</v>
       </c>
@@ -2769,18 +2813,18 @@
       </c>
       <c r="X24" s="3">
         <f>COUNTBLANK(D24:W24)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>159</v>
@@ -2797,7 +2841,9 @@
       <c r="H25" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I25" s="6"/>
+      <c r="I25" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="J25" s="6" t="s">
         <v>159</v>
       </c>
@@ -2810,7 +2856,9 @@
       <c r="M25" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N25" s="6"/>
+      <c r="N25" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O25" s="6" t="s">
         <v>159</v>
       </c>
@@ -2840,17 +2888,17 @@
       </c>
       <c r="X25" s="3">
         <f>COUNTBLANK(D25:W25)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="10" t="s">
         <v>61</v>
       </c>
       <c r="D26" s="6" t="s">
@@ -2881,7 +2929,9 @@
       <c r="M26" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="N26" s="6"/>
+      <c r="N26" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O26" s="6" t="s">
         <v>159</v>
       </c>
@@ -2911,13 +2961,13 @@
       </c>
       <c r="X26" s="3">
         <f>COUNTBLANK(D26:W26)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:X26" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X26">
-      <sortCondition ref="B1:B26"/>
+      <sortCondition ref="C1:C26"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -3104,10 +3154,10 @@
       <c r="A3" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="9" t="s">
         <v>150</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -3176,10 +3226,10 @@
       <c r="A4" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="11" t="s">
         <v>142</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -3399,10 +3449,10 @@
       <c r="A7" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="11" t="s">
         <v>119</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -3770,10 +3820,10 @@
       <c r="A12" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="9" t="s">
         <v>116</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -4135,10 +4185,10 @@
       <c r="A17" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="11" t="s">
         <v>125</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -4210,10 +4260,10 @@
       <c r="A18" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="12" t="s">
         <v>133</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -4283,10 +4333,10 @@
       <c r="A19" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="9" t="s">
         <v>139</v>
       </c>
       <c r="D19" s="5" t="s">
@@ -4431,10 +4481,10 @@
       <c r="A21" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="9" t="s">
         <v>113</v>
       </c>
       <c r="D21" s="5" t="s">
@@ -4581,13 +4631,13 @@
       <c r="C23" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="11"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="15"/>
       <c r="I23" s="5" t="s">
         <v>159</v>
       </c>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DOCENTE\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Profesor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D4DFAC-BF44-4B86-9D8B-BEA77152AB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79079483-0DA1-405F-B077-AA6A784CDCCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pruebas_software" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="165">
   <si>
     <t>Nombre</t>
   </si>
@@ -1200,7 +1200,7 @@
         <v>159</v>
       </c>
       <c r="X2" s="3">
-        <f>COUNTBLANK(D2:W2)</f>
+        <f t="shared" ref="X2:X26" si="0">COUNTBLANK(D2:W2)</f>
         <v>1</v>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         <v>159</v>
       </c>
       <c r="X3" s="3">
-        <f>COUNTBLANK(D3:W3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
         <v>159</v>
       </c>
       <c r="X4" s="3">
-        <f>COUNTBLANK(D4:W4)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
         <v>159</v>
       </c>
       <c r="X5" s="3">
-        <f>COUNTBLANK(D5:W5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
         <v>159</v>
       </c>
       <c r="X6" s="3">
-        <f>COUNTBLANK(D6:W6)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
         <v>159</v>
       </c>
       <c r="X7" s="3">
-        <f>COUNTBLANK(D7:W7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
         <v>159</v>
       </c>
       <c r="X8" s="3">
-        <f>COUNTBLANK(D8:W8)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
         <v>159</v>
       </c>
       <c r="X9" s="3">
-        <f>COUNTBLANK(D9:W9)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
         <v>159</v>
       </c>
       <c r="X10" s="3">
-        <f>COUNTBLANK(D10:W10)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         <v>159</v>
       </c>
       <c r="X11" s="3">
-        <f>COUNTBLANK(D11:W11)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         <v>159</v>
       </c>
       <c r="X12" s="3">
-        <f>COUNTBLANK(D12:W12)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
         <v>159</v>
       </c>
       <c r="X13" s="3">
-        <f>COUNTBLANK(D13:W13)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
         <v>159</v>
       </c>
       <c r="X14" s="3">
-        <f>COUNTBLANK(D14:W14)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2155,7 +2155,7 @@
         <v>159</v>
       </c>
       <c r="X15" s="3">
-        <f>COUNTBLANK(D15:W15)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
         <v>159</v>
       </c>
       <c r="X16" s="3">
-        <f>COUNTBLANK(D16:W16)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
         <v>159</v>
       </c>
       <c r="X17" s="3">
-        <f>COUNTBLANK(D17:W17)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2378,7 +2378,7 @@
         <v>159</v>
       </c>
       <c r="X18" s="3">
-        <f>COUNTBLANK(D18:W18)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
         <v>159</v>
       </c>
       <c r="X19" s="3">
-        <f>COUNTBLANK(D19:W19)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
         <v>159</v>
       </c>
       <c r="X20" s="3">
-        <f>COUNTBLANK(D20:W20)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2599,7 +2599,7 @@
         <v>159</v>
       </c>
       <c r="X21" s="3">
-        <f>COUNTBLANK(D21:W21)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
         <v>159</v>
       </c>
       <c r="X22" s="3">
-        <f>COUNTBLANK(D22:W22)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
         <v>159</v>
       </c>
       <c r="X23" s="3">
-        <f>COUNTBLANK(D23:W23)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
         <v>159</v>
       </c>
       <c r="X24" s="3">
-        <f>COUNTBLANK(D24:W24)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
         <v>159</v>
       </c>
       <c r="X25" s="3">
-        <f>COUNTBLANK(D25:W25)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
         <v>159</v>
       </c>
       <c r="X26" s="3">
-        <f>COUNTBLANK(D26:W26)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -3118,9 +3118,7 @@
       <c r="N2" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="O2" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="O2" s="5"/>
       <c r="P2" s="5" t="s">
         <v>159</v>
       </c>
@@ -3147,7 +3145,7 @@
       </c>
       <c r="X2" s="3">
         <f>COUNTBLANK(D2:W2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -3486,9 +3484,7 @@
         <v>159</v>
       </c>
       <c r="N7" s="8"/>
-      <c r="O7" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="O7" s="5"/>
       <c r="P7" s="5" t="s">
         <v>159</v>
       </c>
@@ -3515,7 +3511,7 @@
       </c>
       <c r="X7" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -3559,9 +3555,7 @@
       <c r="N8" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="O8" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="O8" s="5"/>
       <c r="P8" s="5" t="s">
         <v>159</v>
       </c>
@@ -3588,7 +3582,7 @@
       </c>
       <c r="X8" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -4074,9 +4068,7 @@
       <c r="N15" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="O15" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="O15" s="5"/>
       <c r="P15" s="5" t="s">
         <v>159</v>
       </c>
@@ -4103,7 +4095,7 @@
       </c>
       <c r="X15" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Profesor\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorio\Universitaria_de_colombia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79079483-0DA1-405F-B077-AA6A784CDCCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07BA49BB-0020-4494-B2DE-3A12C95C13EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pruebas_software" sheetId="1" r:id="rId1"/>
@@ -539,7 +539,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -571,6 +571,13 @@
       <u/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="9"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -666,7 +673,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
@@ -694,6 +701,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2859,7 +2869,7 @@
       <c r="N25" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="O25" s="6" t="s">
+      <c r="O25" s="16" t="s">
         <v>159</v>
       </c>
       <c r="P25" s="6" t="s">
@@ -2932,7 +2942,7 @@
       <c r="N26" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="O26" s="6" t="s">
+      <c r="O26" s="16" t="s">
         <v>159</v>
       </c>
       <c r="P26" s="6" t="s">
@@ -2987,6 +2997,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorio\Universitaria_de_colombia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07BA49BB-0020-4494-B2DE-3A12C95C13EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D415F66-6BD4-4E63-8024-3F9C9302AEEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="165">
   <si>
     <t>Nombre</t>
   </si>
@@ -693,6 +693,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -701,9 +704,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1302,15 +1302,21 @@
       <c r="D4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="F4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="6"/>
+      <c r="G4" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="H4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I4" s="6"/>
+      <c r="I4" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="J4" s="6" t="s">
         <v>159</v>
       </c>
@@ -1355,7 +1361,7 @@
       </c>
       <c r="X4" s="3">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
@@ -1477,9 +1483,7 @@
       <c r="O6" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="P6" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="P6" s="6"/>
       <c r="Q6" s="6" t="s">
         <v>159</v>
       </c>
@@ -1503,7 +1507,7 @@
       </c>
       <c r="X6" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -1700,9 +1704,7 @@
       <c r="O9" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="P9" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="P9" s="6"/>
       <c r="Q9" s="6" t="s">
         <v>159</v>
       </c>
@@ -1726,7 +1728,7 @@
       </c>
       <c r="X9" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -2511,9 +2513,7 @@
       <c r="O20" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="P20" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="P20" s="6"/>
       <c r="Q20" s="6" t="s">
         <v>159</v>
       </c>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="X20" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
@@ -2584,9 +2584,7 @@
       <c r="O21" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="P21" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="P21" s="6"/>
       <c r="Q21" s="6" t="s">
         <v>159</v>
       </c>
@@ -2610,7 +2608,7 @@
       </c>
       <c r="X21" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
@@ -2869,7 +2867,7 @@
       <c r="N25" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="O25" s="16" t="s">
+      <c r="O25" s="13" t="s">
         <v>159</v>
       </c>
       <c r="P25" s="6" t="s">
@@ -2942,7 +2940,7 @@
       <c r="N26" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="O26" s="16" t="s">
+      <c r="O26" s="13" t="s">
         <v>159</v>
       </c>
       <c r="P26" s="6" t="s">
@@ -4634,13 +4632,13 @@
       <c r="C23" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="16"/>
       <c r="I23" s="5" t="s">
         <v>159</v>
       </c>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorio\Universitaria_de_colombia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D415F66-6BD4-4E63-8024-3F9C9302AEEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1D5D22-B755-4E8E-94C0-1B8788128262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="165">
   <si>
     <t>Nombre</t>
   </si>
@@ -1188,9 +1188,7 @@
       <c r="P2" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q2" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q2" s="6"/>
       <c r="R2" s="6" t="s">
         <v>159</v>
       </c>
@@ -1211,7 +1209,7 @@
       </c>
       <c r="X2" s="3">
         <f t="shared" ref="X2:X26" si="0">COUNTBLANK(D2:W2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
@@ -1338,9 +1336,7 @@
       <c r="P4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q4" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q4" s="6"/>
       <c r="R4" s="6" t="s">
         <v>159</v>
       </c>
@@ -1361,7 +1357,7 @@
       </c>
       <c r="X4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
@@ -1413,9 +1409,7 @@
       <c r="P5" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q5" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q5" s="6"/>
       <c r="R5" s="6" t="s">
         <v>159</v>
       </c>
@@ -1436,7 +1430,7 @@
       </c>
       <c r="X5" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
@@ -1484,9 +1478,7 @@
         <v>159</v>
       </c>
       <c r="P6" s="6"/>
-      <c r="Q6" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q6" s="6"/>
       <c r="R6" s="6" t="s">
         <v>159</v>
       </c>
@@ -1507,7 +1499,7 @@
       </c>
       <c r="X6" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -1676,7 +1668,9 @@
       <c r="E9" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F9" s="6"/>
+      <c r="F9" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="G9" s="6" t="s">
         <v>159</v>
       </c>
@@ -1704,7 +1698,9 @@
       <c r="O9" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="P9" s="6"/>
+      <c r="P9" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="Q9" s="6" t="s">
         <v>159</v>
       </c>
@@ -1728,7 +1724,7 @@
       </c>
       <c r="X9" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -2072,9 +2068,7 @@
       <c r="P14" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q14" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q14" s="6"/>
       <c r="R14" s="6" t="s">
         <v>159</v>
       </c>
@@ -2095,7 +2089,7 @@
       </c>
       <c r="X14" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -2220,9 +2214,7 @@
       <c r="P16" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q16" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q16" s="6"/>
       <c r="R16" s="6" t="s">
         <v>159</v>
       </c>
@@ -2243,7 +2235,7 @@
       </c>
       <c r="X16" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
@@ -2368,9 +2360,7 @@
       <c r="P18" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q18" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q18" s="6"/>
       <c r="R18" s="6" t="s">
         <v>159</v>
       </c>
@@ -2391,7 +2381,7 @@
       </c>
       <c r="X18" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
@@ -2443,9 +2433,7 @@
       <c r="P19" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q19" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q19" s="6"/>
       <c r="R19" s="6" t="s">
         <v>159</v>
       </c>
@@ -2466,7 +2454,7 @@
       </c>
       <c r="X19" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
@@ -2656,9 +2644,7 @@
       <c r="P22" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q22" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q22" s="6"/>
       <c r="R22" s="6" t="s">
         <v>159</v>
       </c>
@@ -2679,7 +2665,7 @@
       </c>
       <c r="X22" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
@@ -2727,9 +2713,7 @@
       <c r="P23" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q23" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q23" s="6"/>
       <c r="R23" s="6" t="s">
         <v>159</v>
       </c>
@@ -2750,7 +2734,7 @@
       </c>
       <c r="X23" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
@@ -2873,9 +2857,7 @@
       <c r="P25" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q25" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q25" s="6"/>
       <c r="R25" s="6" t="s">
         <v>159</v>
       </c>
@@ -2896,7 +2878,7 @@
       </c>
       <c r="X25" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorio\Universitaria_de_colombia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07BA49BB-0020-4494-B2DE-3A12C95C13EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1D5D22-B755-4E8E-94C0-1B8788128262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="165">
   <si>
     <t>Nombre</t>
   </si>
@@ -693,6 +693,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -701,9 +704,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1188,9 +1188,7 @@
       <c r="P2" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q2" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q2" s="6"/>
       <c r="R2" s="6" t="s">
         <v>159</v>
       </c>
@@ -1211,7 +1209,7 @@
       </c>
       <c r="X2" s="3">
         <f t="shared" ref="X2:X26" si="0">COUNTBLANK(D2:W2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
@@ -1302,15 +1300,21 @@
       <c r="D4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="F4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="6"/>
+      <c r="G4" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="H4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I4" s="6"/>
+      <c r="I4" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="J4" s="6" t="s">
         <v>159</v>
       </c>
@@ -1332,9 +1336,7 @@
       <c r="P4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q4" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q4" s="6"/>
       <c r="R4" s="6" t="s">
         <v>159</v>
       </c>
@@ -1355,7 +1357,7 @@
       </c>
       <c r="X4" s="3">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
@@ -1407,9 +1409,7 @@
       <c r="P5" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q5" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q5" s="6"/>
       <c r="R5" s="6" t="s">
         <v>159</v>
       </c>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="X5" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
@@ -1477,12 +1477,8 @@
       <c r="O6" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="P6" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q6" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
       <c r="R6" s="6" t="s">
         <v>159</v>
       </c>
@@ -1503,7 +1499,7 @@
       </c>
       <c r="X6" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -1672,7 +1668,9 @@
       <c r="E9" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F9" s="6"/>
+      <c r="F9" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="G9" s="6" t="s">
         <v>159</v>
       </c>
@@ -1726,7 +1724,7 @@
       </c>
       <c r="X9" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -2070,9 +2068,7 @@
       <c r="P14" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q14" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q14" s="6"/>
       <c r="R14" s="6" t="s">
         <v>159</v>
       </c>
@@ -2093,7 +2089,7 @@
       </c>
       <c r="X14" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -2218,9 +2214,7 @@
       <c r="P16" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q16" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q16" s="6"/>
       <c r="R16" s="6" t="s">
         <v>159</v>
       </c>
@@ -2241,7 +2235,7 @@
       </c>
       <c r="X16" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
@@ -2366,9 +2360,7 @@
       <c r="P18" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q18" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q18" s="6"/>
       <c r="R18" s="6" t="s">
         <v>159</v>
       </c>
@@ -2389,7 +2381,7 @@
       </c>
       <c r="X18" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
@@ -2441,9 +2433,7 @@
       <c r="P19" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q19" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q19" s="6"/>
       <c r="R19" s="6" t="s">
         <v>159</v>
       </c>
@@ -2464,7 +2454,7 @@
       </c>
       <c r="X19" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
@@ -2511,9 +2501,7 @@
       <c r="O20" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="P20" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="P20" s="6"/>
       <c r="Q20" s="6" t="s">
         <v>159</v>
       </c>
@@ -2537,7 +2525,7 @@
       </c>
       <c r="X20" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
@@ -2584,9 +2572,7 @@
       <c r="O21" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="P21" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="P21" s="6"/>
       <c r="Q21" s="6" t="s">
         <v>159</v>
       </c>
@@ -2610,7 +2596,7 @@
       </c>
       <c r="X21" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
@@ -2658,9 +2644,7 @@
       <c r="P22" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q22" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q22" s="6"/>
       <c r="R22" s="6" t="s">
         <v>159</v>
       </c>
@@ -2681,7 +2665,7 @@
       </c>
       <c r="X22" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
@@ -2729,9 +2713,7 @@
       <c r="P23" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q23" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q23" s="6"/>
       <c r="R23" s="6" t="s">
         <v>159</v>
       </c>
@@ -2752,7 +2734,7 @@
       </c>
       <c r="X23" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
@@ -2869,15 +2851,13 @@
       <c r="N25" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="O25" s="16" t="s">
+      <c r="O25" s="13" t="s">
         <v>159</v>
       </c>
       <c r="P25" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q25" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="Q25" s="6"/>
       <c r="R25" s="6" t="s">
         <v>159</v>
       </c>
@@ -2898,7 +2878,7 @@
       </c>
       <c r="X25" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
@@ -2942,7 +2922,7 @@
       <c r="N26" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="O26" s="16" t="s">
+      <c r="O26" s="13" t="s">
         <v>159</v>
       </c>
       <c r="P26" s="6" t="s">
@@ -4634,13 +4614,13 @@
       <c r="C23" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="16"/>
       <c r="I23" s="5" t="s">
         <v>159</v>
       </c>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorio\Universitaria_de_colombia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Profesor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1D5D22-B755-4E8E-94C0-1B8788128262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD1A42F-A656-432B-B903-84A95C2FB131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pruebas_software" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="169">
   <si>
     <t>Nombre</t>
   </si>
@@ -533,6 +533,18 @@
   </si>
   <si>
     <t>X</t>
+  </si>
+  <si>
+    <t>taller 4</t>
+  </si>
+  <si>
+    <t>taller  modelamiento calse 8</t>
+  </si>
+  <si>
+    <t>my pets</t>
+  </si>
+  <si>
+    <t>taller pagina web</t>
   </si>
 </sst>
 </file>
@@ -608,7 +620,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -668,6 +680,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -687,7 +710,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -704,6 +726,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1216,10 +1241,10 @@
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -1437,10 +1462,10 @@
       <c r="A6" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>73</v>
       </c>
       <c r="D6" s="6" t="s">
@@ -1952,10 +1977,10 @@
       <c r="A13" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>76</v>
       </c>
       <c r="D13" s="6" t="s">
@@ -2096,10 +2121,10 @@
       <c r="A15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -2851,7 +2876,7 @@
       <c r="N25" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="O25" s="13" t="s">
+      <c r="O25" s="12" t="s">
         <v>159</v>
       </c>
       <c r="P25" s="6" t="s">
@@ -2885,10 +2910,10 @@
       <c r="A26" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="9" t="s">
         <v>61</v>
       </c>
       <c r="D26" s="6" t="s">
@@ -2922,7 +2947,7 @@
       <c r="N26" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="O26" s="13" t="s">
+      <c r="O26" s="12" t="s">
         <v>159</v>
       </c>
       <c r="P26" s="6" t="s">
@@ -2983,16 +3008,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC8DBC52-987A-4412-B43F-A9A2EA19A4E3}">
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:AB23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="24" width="4.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="25" width="4.125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="100.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="100.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3065,8 +3093,20 @@
       <c r="X1" s="2" t="s">
         <v>160</v>
       </c>
+      <c r="Y1" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z1" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA1" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB1" s="16" t="s">
+        <v>167</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>157</v>
       </c>
@@ -3138,15 +3178,19 @@
         <f>COUNTBLANK(D2:W2)</f>
         <v>1</v>
       </c>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>150</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -3209,16 +3253,19 @@
         <f t="shared" ref="X3:X22" si="0">COUNTBLANK(D3:W3)</f>
         <v>2</v>
       </c>
-      <c r="Z3" s="7"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>142</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -3285,8 +3332,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>146</v>
       </c>
@@ -3360,8 +3411,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>131</v>
       </c>
@@ -3433,15 +3488,19 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>119</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -3474,8 +3533,12 @@
       <c r="M7" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="N7" s="8"/>
-      <c r="O7" s="5"/>
+      <c r="N7" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="P7" s="5" t="s">
         <v>159</v>
       </c>
@@ -3502,10 +3565,14 @@
       </c>
       <c r="X7" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>106</v>
       </c>
@@ -3556,9 +3623,7 @@
       <c r="R8" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="S8" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="S8" s="5"/>
       <c r="T8" s="5" t="s">
         <v>159</v>
       </c>
@@ -3573,10 +3638,14 @@
       </c>
       <c r="X8" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>100</v>
       </c>
@@ -3650,8 +3719,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>148</v>
       </c>
@@ -3725,8 +3798,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>123</v>
       </c>
@@ -3800,15 +3877,19 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>116</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -3873,8 +3954,12 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>111</v>
       </c>
@@ -3948,8 +4033,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>137</v>
       </c>
@@ -4019,8 +4108,12 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>154</v>
       </c>
@@ -4069,9 +4162,7 @@
       <c r="R15" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="S15" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="S15" s="5"/>
       <c r="T15" s="5" t="s">
         <v>159</v>
       </c>
@@ -4086,10 +4177,14 @@
       </c>
       <c r="X15" s="3">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>126</v>
       </c>
@@ -4163,15 +4258,19 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>125</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -4238,15 +4337,19 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
+      <c r="AB17" s="3"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>133</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -4292,9 +4395,7 @@
       <c r="R18" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="S18" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="S18" s="5"/>
       <c r="T18" s="5" t="s">
         <v>159</v>
       </c>
@@ -4309,17 +4410,21 @@
       </c>
       <c r="X18" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>139</v>
       </c>
       <c r="D19" s="5" t="s">
@@ -4386,8 +4491,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>103</v>
       </c>
@@ -4459,15 +4568,19 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
+      <c r="AB20" s="3"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>113</v>
       </c>
       <c r="D21" s="5" t="s">
@@ -4530,8 +4643,12 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="3"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>109</v>
       </c>
@@ -4605,8 +4722,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
         <v>161</v>
@@ -4614,13 +4735,13 @@
       <c r="C23" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="16"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="15"/>
       <c r="I23" s="5" t="s">
         <v>159</v>
       </c>
@@ -4670,6 +4791,10 @@
         <f>COUNTBLANK(I23:W23)</f>
         <v>0</v>
       </c>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:W1" xr:uid="{AC8DBC52-987A-4412-B43F-A9A2EA19A4E3}">
@@ -4685,7 +4810,7 @@
       <formula>"x"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X1:X1048576">
+  <conditionalFormatting sqref="X1:X1048576 Y1:AB1">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Profesor\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DOCENTE\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD1A42F-A656-432B-B903-84A95C2FB131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9602E98D-02ED-4398-9065-B7FC59E0406E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pruebas_software" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="174">
   <si>
     <t>Nombre</t>
   </si>
@@ -545,6 +545,21 @@
   </si>
   <si>
     <t>taller pagina web</t>
+  </si>
+  <si>
+    <t>taller  s4</t>
+  </si>
+  <si>
+    <t>tarea s5</t>
+  </si>
+  <si>
+    <t>tarea s7</t>
+  </si>
+  <si>
+    <t>tarea s11</t>
+  </si>
+  <si>
+    <t>tarea s15</t>
   </si>
 </sst>
 </file>
@@ -696,7 +711,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
@@ -717,6 +732,9 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1083,16 +1101,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
     <col min="4" max="24" width="4.125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5" customWidth="1"/>
+    <col min="26" max="28" width="5.5" customWidth="1"/>
+    <col min="29" max="29" width="4.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="100.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="100.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1165,8 +1186,23 @@
       <c r="X1" s="2" t="s">
         <v>158</v>
       </c>
+      <c r="Y1" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z1" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA1" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB1" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="AC1" s="17" t="s">
+        <v>173</v>
+      </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>71</v>
       </c>
@@ -1236,8 +1272,12 @@
         <f t="shared" ref="X2:X26" si="0">COUNTBLANK(D2:W2)</f>
         <v>2</v>
       </c>
+      <c r="Y2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -1311,8 +1351,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -1384,8 +1429,13 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
@@ -1457,8 +1507,13 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>74</v>
       </c>
@@ -1507,9 +1562,7 @@
       <c r="R6" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="S6" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="S6" s="6"/>
       <c r="T6" s="6" t="s">
         <v>159</v>
       </c>
@@ -1524,10 +1577,15 @@
       </c>
       <c r="X6" s="3">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -1601,8 +1659,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="3"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>59</v>
       </c>
@@ -1676,8 +1739,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="3"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1751,8 +1819,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3"/>
+      <c r="AC9" s="3"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>47</v>
       </c>
@@ -1824,8 +1897,13 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="3"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
@@ -1897,8 +1975,13 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>56</v>
       </c>
@@ -1972,8 +2055,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="3"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>77</v>
       </c>
@@ -2045,8 +2133,13 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3"/>
+      <c r="AC13" s="3"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>53</v>
       </c>
@@ -2116,8 +2209,13 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3"/>
+      <c r="AC14" s="3"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>26</v>
       </c>
@@ -2170,9 +2268,7 @@
       <c r="R15" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="S15" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="S15" s="6"/>
       <c r="T15" s="6" t="s">
         <v>159</v>
       </c>
@@ -2187,10 +2283,15 @@
       </c>
       <c r="X15" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="3"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>32</v>
       </c>
@@ -2262,8 +2363,13 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
@@ -2337,8 +2443,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
+      <c r="AB17" s="3"/>
+      <c r="AC17" s="3"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>29</v>
       </c>
@@ -2408,8 +2519,13 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3"/>
+      <c r="AC18" s="3"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>50</v>
       </c>
@@ -2481,8 +2597,13 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>35</v>
       </c>
@@ -2552,8 +2673,13 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
+      <c r="AB20" s="3"/>
+      <c r="AC20" s="3"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>65</v>
       </c>
@@ -2623,8 +2749,13 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="3"/>
+      <c r="AC21" s="3"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>68</v>
       </c>
@@ -2692,8 +2823,13 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>23</v>
       </c>
@@ -2761,8 +2897,13 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="3"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>8</v>
       </c>
@@ -2832,8 +2973,13 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="3"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>44</v>
       </c>
@@ -2905,8 +3051,13 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="3"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>62</v>
       </c>
@@ -2978,6 +3129,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
+      <c r="AB26" s="3"/>
+      <c r="AC26" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:X26" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -2991,7 +3147,7 @@
       <formula>NOT(ISERROR(SEARCH("x",D2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X1:X1048576">
+  <conditionalFormatting sqref="X1:X1048576 Y1:AC1">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -3093,16 +3249,16 @@
       <c r="X1" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="Y1" s="16" t="s">
+      <c r="Y1" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="Z1" s="16" t="s">
+      <c r="Z1" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="AA1" s="16" t="s">
+      <c r="AA1" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="AB1" s="16" t="s">
+      <c r="AB1" s="13" t="s">
         <v>167</v>
       </c>
     </row>
@@ -4735,13 +4891,13 @@
       <c r="C23" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="16"/>
       <c r="I23" s="5" t="s">
         <v>159</v>
       </c>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DOCENTE\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorio\Universitaria_de_colombia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9602E98D-02ED-4398-9065-B7FC59E0406E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C12E5C-93D3-4C11-B1C6-A06CBB7B3D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pruebas_software" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="174">
   <si>
     <t>Nombre</t>
   </si>
@@ -736,6 +736,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -744,9 +745,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1101,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
@@ -1186,19 +1184,19 @@
       <c r="X1" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="Y1" s="17" t="s">
+      <c r="Y1" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="Z1" s="17" t="s">
+      <c r="Z1" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="AA1" s="17" t="s">
+      <c r="AA1" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="AB1" s="17" t="s">
+      <c r="AB1" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AC1" s="17" t="s">
+      <c r="AC1" s="13" t="s">
         <v>173</v>
       </c>
     </row>
@@ -1256,9 +1254,7 @@
       <c r="S2" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="T2" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="T2" s="6"/>
       <c r="U2" s="6" t="s">
         <v>159</v>
       </c>
@@ -1270,7 +1266,7 @@
       </c>
       <c r="X2" s="3">
         <f t="shared" ref="X2:X26" si="0">COUNTBLANK(D2:W2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2" s="3"/>
       <c r="AA2" s="3"/>
@@ -1413,9 +1409,7 @@
       <c r="S4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="T4" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="T4" s="6"/>
       <c r="U4" s="6" t="s">
         <v>159</v>
       </c>
@@ -1427,7 +1421,7 @@
       </c>
       <c r="X4" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
@@ -1557,12 +1551,18 @@
       <c r="O6" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
+      <c r="P6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="R6" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="S6" s="6"/>
+      <c r="S6" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="T6" s="6" t="s">
         <v>159</v>
       </c>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="X6" s="3">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
@@ -1640,7 +1640,7 @@
       <c r="R7" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="S7" s="6" t="s">
+      <c r="S7" s="12" t="s">
         <v>159</v>
       </c>
       <c r="T7" s="6" t="s">
@@ -1803,9 +1803,7 @@
       <c r="S9" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="T9" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="T9" s="6"/>
       <c r="U9" s="6" t="s">
         <v>159</v>
       </c>
@@ -1817,7 +1815,7 @@
       </c>
       <c r="X9" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
@@ -2117,7 +2115,7 @@
       <c r="S13" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="T13" s="6" t="s">
+      <c r="T13" s="12" t="s">
         <v>159</v>
       </c>
       <c r="U13" s="6" t="s">
@@ -2347,9 +2345,7 @@
       <c r="S16" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="T16" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="T16" s="6"/>
       <c r="U16" s="6" t="s">
         <v>159</v>
       </c>
@@ -2361,7 +2357,7 @@
       </c>
       <c r="X16" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
@@ -3134,6 +3130,9 @@
       <c r="AA26" s="3"/>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="T27" s="14"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:X26" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -4891,13 +4890,13 @@
       <c r="C23" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="17"/>
       <c r="I23" s="5" t="s">
         <v>159</v>
       </c>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorio\Universitaria_de_colombia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Profesor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C12E5C-93D3-4C11-B1C6-A06CBB7B3D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF58A5FD-ED3E-40FE-9CFF-1A6EBBBE5D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pruebas_software" sheetId="1" r:id="rId1"/>
     <sheet name="Lenguajes_ultima_g" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Lenguajes_ultima_g!$A$1:$W$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Lenguajes_ultima_g!$A$1:$AB$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Pruebas_software!$A$1:$X$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="173">
   <si>
     <t>Nombre</t>
   </si>
@@ -527,9 +527,6 @@
   </si>
   <si>
     <t>caraballo</t>
-  </si>
-  <si>
-    <t>matricula tardia</t>
   </si>
   <si>
     <t>X</t>
@@ -566,7 +563,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -608,6 +605,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF666666"/>
+      <name val="Montserrat"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -635,7 +638,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -647,43 +650,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -733,18 +699,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1185,19 +1147,19 @@
         <v>158</v>
       </c>
       <c r="Y1" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z1" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="Z1" s="13" t="s">
+      <c r="AA1" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="AA1" s="13" t="s">
+      <c r="AB1" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="AB1" s="13" t="s">
+      <c r="AC1" s="13" t="s">
         <v>172</v>
-      </c>
-      <c r="AC1" s="13" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
@@ -1265,7 +1227,6 @@
         <v>159</v>
       </c>
       <c r="X2" s="3">
-        <f t="shared" ref="X2:X26" si="0">COUNTBLANK(D2:W2)</f>
         <v>3</v>
       </c>
       <c r="Y2" s="3"/>
@@ -1344,7 +1305,6 @@
         <v>159</v>
       </c>
       <c r="X3" s="3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y3" s="3"/>
@@ -1420,7 +1380,6 @@
         <v>159</v>
       </c>
       <c r="X4" s="3">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Y4" s="3"/>
@@ -1498,7 +1457,6 @@
         <v>159</v>
       </c>
       <c r="X5" s="3">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y5" s="3"/>
@@ -1576,7 +1534,6 @@
         <v>159</v>
       </c>
       <c r="X6" s="3">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y6" s="3"/>
@@ -1656,7 +1613,6 @@
         <v>159</v>
       </c>
       <c r="X7" s="3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y7" s="3"/>
@@ -1736,7 +1692,6 @@
         <v>159</v>
       </c>
       <c r="X8" s="3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y8" s="3"/>
@@ -1814,7 +1769,6 @@
         <v>159</v>
       </c>
       <c r="X9" s="3">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y9" s="3"/>
@@ -1892,7 +1846,6 @@
         <v>159</v>
       </c>
       <c r="X10" s="3">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y10" s="3"/>
@@ -1970,7 +1923,6 @@
         <v>159</v>
       </c>
       <c r="X11" s="3">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y11" s="3"/>
@@ -2050,7 +2002,6 @@
         <v>159</v>
       </c>
       <c r="X12" s="3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y12" s="3"/>
@@ -2128,7 +2079,6 @@
         <v>159</v>
       </c>
       <c r="X13" s="3">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y13" s="3"/>
@@ -2204,7 +2154,6 @@
         <v>159</v>
       </c>
       <c r="X14" s="3">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Y14" s="3"/>
@@ -2280,7 +2229,6 @@
         <v>159</v>
       </c>
       <c r="X15" s="3">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Y15" s="3"/>
@@ -2356,7 +2304,6 @@
         <v>159</v>
       </c>
       <c r="X16" s="3">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Y16" s="3"/>
@@ -2436,7 +2383,6 @@
         <v>159</v>
       </c>
       <c r="X17" s="3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y17" s="3"/>
@@ -2512,7 +2458,6 @@
         <v>159</v>
       </c>
       <c r="X18" s="3">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Y18" s="3"/>
@@ -2590,7 +2535,6 @@
         <v>159</v>
       </c>
       <c r="X19" s="3">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y19" s="3"/>
@@ -2666,7 +2610,6 @@
         <v>159</v>
       </c>
       <c r="X20" s="3">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Y20" s="3"/>
@@ -2742,7 +2685,6 @@
         <v>159</v>
       </c>
       <c r="X21" s="3">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Y21" s="3"/>
@@ -2816,7 +2758,6 @@
         <v>159</v>
       </c>
       <c r="X22" s="3">
-        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="Y22" s="3"/>
@@ -2890,7 +2831,6 @@
         <v>159</v>
       </c>
       <c r="X23" s="3">
-        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="Y23" s="3"/>
@@ -2966,7 +2906,6 @@
         <v>159</v>
       </c>
       <c r="X24" s="3">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Y24" s="3"/>
@@ -3044,7 +2983,6 @@
         <v>159</v>
       </c>
       <c r="X25" s="3">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y25" s="3"/>
@@ -3122,7 +3060,6 @@
         <v>159</v>
       </c>
       <c r="X26" s="3">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y26" s="3"/>
@@ -3163,7 +3100,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC8DBC52-987A-4412-B43F-A9A2EA19A4E3}">
-  <dimension ref="A1:AB23"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.375" bestFit="1" customWidth="1"/>
@@ -3175,7 +3112,7 @@
     <col min="28" max="28" width="4.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="100.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="100.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3249,19 +3186,20 @@
         <v>160</v>
       </c>
       <c r="Y1" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z1" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="Z1" s="13" t="s">
+      <c r="AA1" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB1" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="AA1" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB1" s="13" t="s">
-        <v>167</v>
-      </c>
+      <c r="AC1" s="14"/>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>157</v>
       </c>
@@ -3321,7 +3259,7 @@
         <v>159</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V2" s="5" t="s">
         <v>159</v>
@@ -3335,18 +3273,22 @@
       </c>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
+      <c r="AA2" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>163</v>
+      </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>159</v>
@@ -3366,7 +3308,9 @@
       <c r="I3" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="J3" s="5"/>
+      <c r="J3" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="K3" s="5" t="s">
         <v>159</v>
       </c>
@@ -3376,7 +3320,9 @@
       <c r="M3" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="N3" s="5"/>
+      <c r="N3" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="O3" s="5" t="s">
         <v>159</v>
       </c>
@@ -3396,7 +3342,7 @@
         <v>159</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V3" s="5" t="s">
         <v>159</v>
@@ -3405,23 +3351,27 @@
         <v>159</v>
       </c>
       <c r="X3" s="3">
-        <f t="shared" ref="X3:X22" si="0">COUNTBLANK(D3:W3)</f>
-        <v>2</v>
+        <f>COUNTBLANK(D3:W3)</f>
+        <v>0</v>
       </c>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
+      <c r="AA3" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>163</v>
+      </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>142</v>
+        <v>106</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>159</v>
@@ -3447,18 +3397,14 @@
       <c r="K4" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="L4" s="5"/>
       <c r="M4" s="5" t="s">
         <v>159</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="O4" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="O4" s="5"/>
       <c r="P4" s="5" t="s">
         <v>159</v>
       </c>
@@ -3468,14 +3414,12 @@
       <c r="R4" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="S4" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="S4" s="5"/>
       <c r="T4" s="5" t="s">
         <v>159</v>
       </c>
       <c r="U4" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V4" s="5" t="s">
         <v>159</v>
@@ -3484,23 +3428,27 @@
         <v>159</v>
       </c>
       <c r="X4" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D4:W4)</f>
+        <v>3</v>
       </c>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
+      <c r="AA4" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>163</v>
+      </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>159</v>
@@ -3554,7 +3502,7 @@
         <v>159</v>
       </c>
       <c r="U5" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V5" s="5" t="s">
         <v>159</v>
@@ -3563,23 +3511,27 @@
         <v>159</v>
       </c>
       <c r="X5" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D5:W5)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
+      <c r="AA5" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB5" s="3" t="s">
+        <v>163</v>
+      </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>159</v>
@@ -3593,7 +3545,9 @@
       <c r="G6" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H6" s="5"/>
+      <c r="H6" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="I6" s="5" t="s">
         <v>159</v>
       </c>
@@ -3631,7 +3585,7 @@
         <v>159</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V6" s="5" t="s">
         <v>159</v>
@@ -3640,23 +3594,27 @@
         <v>159</v>
       </c>
       <c r="X6" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTBLANK(D6:W6)</f>
+        <v>0</v>
       </c>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
+      <c r="AA6" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB6" s="3" t="s">
+        <v>163</v>
+      </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>119</v>
+        <v>137</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>136</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>159</v>
@@ -3667,12 +3625,8 @@
       <c r="F7" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
         <v>159</v>
       </c>
@@ -3688,7 +3642,7 @@
       <c r="M7" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="5" t="s">
         <v>159</v>
       </c>
       <c r="O7" s="5" t="s">
@@ -3710,7 +3664,7 @@
         <v>159</v>
       </c>
       <c r="U7" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V7" s="5" t="s">
         <v>159</v>
@@ -3719,39 +3673,39 @@
         <v>159</v>
       </c>
       <c r="X7" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D7:W7)</f>
+        <v>2</v>
       </c>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
-      <c r="AB7" s="3"/>
+      <c r="AA7" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>163</v>
+      </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="E8" s="5"/>
       <c r="F8" s="5" t="s">
         <v>159</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="H8" s="5"/>
       <c r="I8" s="5" t="s">
         <v>159</v>
       </c>
@@ -3761,7 +3715,9 @@
       <c r="K8" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L8" s="5"/>
+      <c r="L8" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="M8" s="5" t="s">
         <v>159</v>
       </c>
@@ -3778,12 +3734,14 @@
       <c r="R8" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="S8" s="5"/>
+      <c r="S8" s="5" t="s">
+        <v>163</v>
+      </c>
       <c r="T8" s="5" t="s">
         <v>159</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V8" s="5" t="s">
         <v>159</v>
@@ -3792,23 +3750,27 @@
         <v>159</v>
       </c>
       <c r="X8" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D8:W8)</f>
         <v>3</v>
       </c>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
+      <c r="AA8" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>163</v>
+      </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>159</v>
@@ -3862,7 +3824,7 @@
         <v>159</v>
       </c>
       <c r="U9" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V9" s="5" t="s">
         <v>159</v>
@@ -3871,23 +3833,27 @@
         <v>159</v>
       </c>
       <c r="X9" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D9:W9)</f>
         <v>0</v>
       </c>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
-      <c r="AB9" s="3"/>
+      <c r="AA9" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>163</v>
+      </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>147</v>
+        <v>134</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>133</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>159</v>
@@ -3895,9 +3861,7 @@
       <c r="E10" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="F10" s="5"/>
       <c r="G10" s="5" t="s">
         <v>159</v>
       </c>
@@ -3935,13 +3899,13 @@
         <v>159</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="T10" s="5" t="s">
         <v>159</v>
       </c>
       <c r="U10" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V10" s="5" t="s">
         <v>159</v>
@@ -3950,23 +3914,27 @@
         <v>159</v>
       </c>
       <c r="X10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D10:W10)</f>
+        <v>1</v>
       </c>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
-      <c r="AB10" s="3"/>
+      <c r="AA10" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>163</v>
+      </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>159</v>
@@ -3992,9 +3960,7 @@
       <c r="K11" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L11" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="L11" s="5"/>
       <c r="M11" s="5" t="s">
         <v>159</v>
       </c>
@@ -4019,9 +3985,7 @@
       <c r="T11" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="U11" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="U11" s="5"/>
       <c r="V11" s="5" t="s">
         <v>159</v>
       </c>
@@ -4029,23 +3993,27 @@
         <v>159</v>
       </c>
       <c r="X11" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D11:W11)</f>
+        <v>2</v>
       </c>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
-      <c r="AB11" s="3"/>
+      <c r="AA11" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB11" s="3" t="s">
+        <v>163</v>
+      </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>159</v>
@@ -4056,22 +4024,20 @@
       <c r="F12" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="I12" s="5"/>
+      <c r="I12" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="J12" s="5" t="s">
         <v>159</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L12" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="L12" s="5"/>
       <c r="M12" s="5" t="s">
         <v>159</v>
       </c>
@@ -4097,7 +4063,7 @@
         <v>159</v>
       </c>
       <c r="U12" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V12" s="5" t="s">
         <v>159</v>
@@ -4106,39 +4072,31 @@
         <v>159</v>
       </c>
       <c r="X12" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTBLANK(D12:W12)</f>
+        <v>2</v>
       </c>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
-      <c r="AB12" s="3"/>
+      <c r="AA12" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>163</v>
+      </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>111</v>
-      </c>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>159</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
       <c r="I13" s="5" t="s">
         <v>159</v>
       </c>
@@ -4185,23 +4143,29 @@
         <v>159</v>
       </c>
       <c r="X13" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(I13:W13)</f>
         <v>0</v>
       </c>
-      <c r="Y13" s="3"/>
+      <c r="Y13" s="3" t="s">
+        <v>159</v>
+      </c>
       <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
-      <c r="AB13" s="3"/>
+      <c r="AA13" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB13" s="3" t="s">
+        <v>159</v>
+      </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>136</v>
+        <v>143</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>142</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>159</v>
@@ -4212,8 +4176,12 @@
       <c r="F14" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
+      <c r="G14" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="I14" s="5" t="s">
         <v>159</v>
       </c>
@@ -4251,7 +4219,7 @@
         <v>159</v>
       </c>
       <c r="U14" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V14" s="5" t="s">
         <v>159</v>
@@ -4260,35 +4228,43 @@
         <v>159</v>
       </c>
       <c r="X14" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>COUNTBLANK(D14:W14)</f>
+        <v>0</v>
       </c>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
-      <c r="AB14" s="3"/>
+      <c r="AA14" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>159</v>
+      </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>153</v>
+        <v>120</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>119</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="F15" s="5" t="s">
         <v>159</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H15" s="5"/>
+      <c r="H15" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="I15" s="5" t="s">
         <v>159</v>
       </c>
@@ -4304,10 +4280,12 @@
       <c r="M15" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="N15" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="O15" s="5"/>
+      <c r="N15" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="P15" s="5" t="s">
         <v>159</v>
       </c>
@@ -4317,12 +4295,14 @@
       <c r="R15" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="S15" s="5"/>
+      <c r="S15" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="T15" s="5" t="s">
         <v>159</v>
       </c>
       <c r="U15" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V15" s="5" t="s">
         <v>159</v>
@@ -4331,22 +4311,26 @@
         <v>159</v>
       </c>
       <c r="X15" s="3">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>COUNTBLANK(D15:W15)</f>
+        <v>0</v>
       </c>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
-      <c r="AB15" s="3"/>
+      <c r="AA15" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB15" s="3" t="s">
+        <v>159</v>
+      </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C16" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>125</v>
       </c>
       <c r="D16" s="5" t="s">
@@ -4401,7 +4385,7 @@
         <v>159</v>
       </c>
       <c r="U16" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V16" s="5" t="s">
         <v>159</v>
@@ -4410,23 +4394,27 @@
         <v>159</v>
       </c>
       <c r="X16" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D16:W16)</f>
         <v>0</v>
       </c>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
-      <c r="AB16" s="3"/>
+      <c r="AA16" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB16" s="3" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>125</v>
+        <v>131</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>159</v>
@@ -4440,9 +4428,7 @@
       <c r="G17" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H17" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="H17" s="5"/>
       <c r="I17" s="5" t="s">
         <v>159</v>
       </c>
@@ -4480,7 +4466,7 @@
         <v>159</v>
       </c>
       <c r="U17" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V17" s="5" t="s">
         <v>159</v>
@@ -4489,23 +4475,27 @@
         <v>159</v>
       </c>
       <c r="X17" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D17:W17)</f>
+        <v>1</v>
       </c>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
-      <c r="AA17" s="3"/>
-      <c r="AB17" s="3"/>
+      <c r="AA17" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB17" s="3" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>133</v>
+        <v>109</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>159</v>
@@ -4513,7 +4503,9 @@
       <c r="E18" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="F18" s="5"/>
+      <c r="F18" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="G18" s="5" t="s">
         <v>159</v>
       </c>
@@ -4550,12 +4542,14 @@
       <c r="R18" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="S18" s="5"/>
+      <c r="S18" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="T18" s="5" t="s">
         <v>159</v>
       </c>
       <c r="U18" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V18" s="5" t="s">
         <v>159</v>
@@ -4564,23 +4558,27 @@
         <v>159</v>
       </c>
       <c r="X18" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>COUNTBLANK(D18:W18)</f>
+        <v>0</v>
       </c>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
-      <c r="AA18" s="3"/>
-      <c r="AB18" s="3"/>
+      <c r="AA18" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB18" s="3" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>159</v>
@@ -4600,9 +4598,7 @@
       <c r="I19" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="J19" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
         <v>159</v>
       </c>
@@ -4612,9 +4608,7 @@
       <c r="M19" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="N19" s="5" t="s">
-        <v>164</v>
-      </c>
+      <c r="N19" s="5"/>
       <c r="O19" s="5" t="s">
         <v>159</v>
       </c>
@@ -4634,7 +4628,7 @@
         <v>159</v>
       </c>
       <c r="U19" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V19" s="5" t="s">
         <v>159</v>
@@ -4643,23 +4637,27 @@
         <v>159</v>
       </c>
       <c r="X19" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTBLANK(D19:W19)</f>
+        <v>2</v>
       </c>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
-      <c r="AB19" s="3"/>
+      <c r="AA19" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB19" s="5" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>159</v>
@@ -4685,7 +4683,9 @@
       <c r="K20" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L20" s="5"/>
+      <c r="L20" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="M20" s="5" t="s">
         <v>159</v>
       </c>
@@ -4711,7 +4711,7 @@
         <v>159</v>
       </c>
       <c r="U20" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V20" s="5" t="s">
         <v>159</v>
@@ -4720,23 +4720,25 @@
         <v>159</v>
       </c>
       <c r="X20" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTBLANK(D20:W20)</f>
+        <v>0</v>
       </c>
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
-      <c r="AA20" s="3"/>
-      <c r="AB20" s="3"/>
+      <c r="AA20" s="16"/>
+      <c r="AB20" s="3" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>159</v>
@@ -4747,20 +4749,22 @@
       <c r="F21" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="G21" s="5"/>
+      <c r="G21" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="H21" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="I21" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="I21" s="5"/>
       <c r="J21" s="5" t="s">
         <v>159</v>
       </c>
       <c r="K21" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L21" s="5"/>
+      <c r="L21" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="M21" s="5" t="s">
         <v>159</v>
       </c>
@@ -4786,7 +4790,7 @@
         <v>159</v>
       </c>
       <c r="U21" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V21" s="5" t="s">
         <v>159</v>
@@ -4795,8 +4799,8 @@
         <v>159</v>
       </c>
       <c r="X21" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>COUNTBLANK(D21:W21)</f>
+        <v>1</v>
       </c>
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
@@ -4805,13 +4809,13 @@
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>159</v>
@@ -4865,7 +4869,7 @@
         <v>159</v>
       </c>
       <c r="U22" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V22" s="5" t="s">
         <v>159</v>
@@ -4874,47 +4878,61 @@
         <v>159</v>
       </c>
       <c r="X22" s="3">
-        <f t="shared" si="0"/>
+        <f>COUNTBLANK(D22:W22)</f>
         <v>0</v>
       </c>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
-      <c r="AA22" s="3"/>
-      <c r="AB22" s="3"/>
+      <c r="AA22" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB22" s="5" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="D23" s="15" t="s">
+      <c r="A23" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="N23" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>159</v>
-      </c>
       <c r="O23" s="5" t="s">
         <v>159</v>
       </c>
@@ -4934,7 +4952,7 @@
         <v>159</v>
       </c>
       <c r="U23" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V23" s="5" t="s">
         <v>159</v>
@@ -4943,24 +4961,25 @@
         <v>159</v>
       </c>
       <c r="X23" s="3">
-        <f>COUNTBLANK(I23:W23)</f>
+        <f>COUNTBLANK(D23:W23)</f>
         <v>0</v>
       </c>
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
-      <c r="AA23" s="3"/>
-      <c r="AB23" s="3"/>
+      <c r="AA23" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB23" s="3" t="s">
+        <v>159</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W1" xr:uid="{AC8DBC52-987A-4412-B43F-A9A2EA19A4E3}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W23">
-      <sortCondition ref="B1"/>
+  <autoFilter ref="A1:AB23" xr:uid="{AC8DBC52-987A-4412-B43F-A9A2EA19A4E3}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB23">
+      <sortCondition ref="AB1:AB23"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="1">
-    <mergeCell ref="D23:H23"/>
-  </mergeCells>
-  <conditionalFormatting sqref="D2:W22 D23 I23:W23">
+  <conditionalFormatting sqref="D2:W23">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"x"</formula>
     </cfRule>
